--- a/ehs_courses_matched.xlsx
+++ b/ehs_courses_matched.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2274" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2274" uniqueCount="604">
   <si>
     <t>Course Number</t>
   </si>
@@ -73,7 +73,7 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>Science</t>
+    <t>Elective</t>
   </si>
   <si>
     <t>ROP Civil engineering has a significant role in the life of every human being, though one may not truly sense its importance in our daily routines. Architecture is the art / practice of designing and constructing buildings. To help students explore these career fields, students learn about various aspects of civil engineering and architecture and apply their knowledge to the design and development of residential and commercial properties and structures. In addition, students use 3D design software to design and document solutions for major course projects. Students communicate and present solutions to their peers and members of a professional community of engineers and architects. This course is a specialization-level course designed to follow the Project Lead the Way Engineering foundation courses.</t>
@@ -94,6 +94,9 @@
     <t>No</t>
   </si>
   <si>
+    <t>Physical Science</t>
+  </si>
+  <si>
     <t>How are things made? What processes go into creating products? Is the process for making a water bottle the same as it is for a musical instrument? How do assembly lines work? How has automation changed the face of manufacturing? While students discover the answers to these questions, they're learning about the history of manufacturing, robotics and automation, manufacturing processes, computer modeling, manufacturing equipment, and flexible manufacturing systems. This course is a specialized-level course designed to follow the Project Lead the Way Engineering foundation courses.</t>
   </si>
   <si>
@@ -115,9 +118,6 @@
     <t>(717015, 717016, 713785, 713737)</t>
   </si>
   <si>
-    <t>Elective</t>
-  </si>
-  <si>
     <t>PLTW Capstone is a completer course for students in a PLTW pathway: computer science, engineering, and biomedical science come together in PLTW Capstone as student teams pool resources to identify an issue or problem of interest and then research, design, and test a solution, ultimately presenting their solution to a panel of professionals. Students work with their team, drawing on the strengths and skills of each member, as they prepare themselves for the interdisciplinary collaboration required for success in college and career.</t>
   </si>
   <si>
@@ -292,7 +292,10 @@
     <t>Contemporary Health</t>
   </si>
   <si>
-    <t>Your course description for Contemporary Health is not provided in the text.</t>
+    <t>Health</t>
+  </si>
+  <si>
+    <t>Contemporary Health is a year-long skills-based course that explores the five components of health: Social, Emotional, Mental, Financial, Emotional, and Physical Health through the lens of each student's own personal identity. Students will obtain accurate information, develop lifelong positive health-related attitudes and behaviors, and explore options related to their personal health, and college and career choices. Each class will also have dedicated junior and senior mentors as a part of our Freshman Mentor Program that will help support freshmen while gaining comfort with their new surroundings in high school, as well as help build foundational skills for lifelong success. Students will practice and pursue mastery in: analyzing influences, accessing valid information, interpersonal communication, decision making, goal setting, practicing health-enhancing behaviors, and health promotion (the seven standards from the California Health Framework).</t>
   </si>
   <si>
     <t>Homework assigned a few times per unit but not on a daily basis</t>
@@ -370,7 +373,7 @@
     <t>Culinary Arts</t>
   </si>
   <si>
-    <t>Art</t>
+    <t>Visual/Performing Arts</t>
   </si>
   <si>
     <t>This basic foods course covers kitchen principles, recipe skills, guidelines for good nutrition, and mealtime customs as well as to develop skills in the kitchen.  Students learn the principles of preparing quick breads, cookies, salads, soups, sandwiches, casseroles, dairy products, and eggs.  Emphasis is on making healthy food choices and safeguarding the family’s health.  Areas of food preparation in the second semester also include meat, poultry, pasta, fruits and  vegetables, breads, cakes, and candies.  Career opportunities are explored.  Food preparation and service is a very important part of this class. As students study food preparation, they explore careers in the food industry.  This is a hands-on class. There is a $50 suggested donation per year for consumable materials.</t>
@@ -382,7 +385,7 @@
     <t>Ethnic Studies 1</t>
   </si>
   <si>
-    <t>Fulfills the district Ethnic Studies graduation requirement for students graduating in 2028 and beyond</t>
+    <t>Ethnic Studies</t>
   </si>
   <si>
     <t>In Ethnic Studies students will study the histories and cultures of Asian Americans, Pacific Islanders, Chicanx/Latinx, American Indians/Native Americans, Black/African Americans and other historically marginalized groups and analyze systems of oppression to promote solidarity and community transformation.</t>
@@ -394,9 +397,6 @@
     <t>World History</t>
   </si>
   <si>
-    <t>Social Science</t>
-  </si>
-  <si>
     <t>Students examine major turning points in the shaping of the modern world.  First semester is spent looking at the expansion of the West (Europe) and the growing interdependence of people and cultures throughout the world, including both world wars. Second semester continues the study of the 20th and 21st centuries.  Current events, class activities, projects, historical writing, visual and auditory strategies are used to promote class discussions and critical thinking skills.  Major areas to be studied are Rising Tide of Revolutions, Industrialization and Its Impact, Western Imperialism, World War II, Civilizations in Crisis (1882-1945) and the Contemporary World (1945 to present). Homework for this course is an invaluable tool used to introduce, reinforce, and help with comprehension with respect to course material.</t>
   </si>
   <si>
@@ -412,13 +412,16 @@
     <t>United States History</t>
   </si>
   <si>
+    <t>US History</t>
+  </si>
+  <si>
     <t>United States History offers a broad curriculum with emphasis on vitalizing history as a link between past and present.  Students examine the chronological background of significant events and critical turning points in U. S. history, identify individuals/groups who made major contributions to the political, economic, social, and cultural development in a given  period; define the basic values and principles of our constitutional system and the pluralistic nature of our states and nation; recognize the historical development of the United States as a world power; and understand the social, political, and economic stance of the United States in the world community.  Emphasis in U.S. History is on critical thinking skills attained through class lectures, discussions, activities, projects, historical writing and argumentative essays.</t>
   </si>
   <si>
     <t>AP United States History (APUSH)</t>
   </si>
   <si>
-    <t>Graduation: Fulfills second year of Social Science requirement College Prep: UC/CSU “A” area - History credit with a grade of “C” or better , weighted course</t>
+    <t>Students build an understanding of the economic, political, and social changes that have occurred in United States history.  This course encourages students to weigh evidence and interpret problems presented by historians.Through assessment and critical analysis of historical documents and interpretations of them, students learn to analyze data, form conclusions, and present well-reasoned, persuasive arguments in written form.  Homework for this course is an invaluable tool used to introduce, reinforce, and help with comprehension with respect to course material.</t>
   </si>
   <si>
     <t>AP United States Government and Politics</t>
@@ -436,7 +439,7 @@
     <t>AP African American Studies</t>
   </si>
   <si>
-    <t>College Prep: UC/CSU “G” area elective credit with a grade of “C” or better</t>
+    <t>AP African American Studies is an interdisciplinary course that examines the diversity of African American experiences through direct encounters with authentic and varied sources. Students explore key topics that extend from early African kingdoms to the ongoing challenges and achievements of the contemporary moment. Given the interdisciplinary character of African American studies, students in the course will develop skills across multiple fields, with an emphasis on developing historical, literary, visual, and data analysis skills. This course foregrounds a study of the diversity of Black communities in the United States within the broader context of Africa and the African diaspora.</t>
   </si>
   <si>
     <t>Civics</t>
@@ -655,7 +658,7 @@
     <t>AP Seminar (AP Capstone Year 1) (HP)</t>
   </si>
   <si>
-    <t>Graduation: Fulfills CSU/UC "G" elective requirement with a grade of “C” or better - weighted grade in grades 10 - 12.</t>
+    <t xml:space="preserve">AP Seminar is a college level course designed around skill development. It is the first course in the AP Capstone sequence. Students learn to master writing, researching, and presenting while analyzing local and global issues through various lenses. Throughout the course, students select four different topics and generate research questions they will use to complete projects, essays, reports, presentations, and discussions. Students are encouraged to commit to the full two-year AP Capstone sequence; however, AP Seminar can be taken as a standalone elective. Students who earn scores of 3 or higher in AP Seminar and AP Research and on four additional AP Exams of their choosing will receive the AP Capstone Diploma.  Students who earn scores of 3 or higher in AP Seminar and AP Research but not on four additional AP Exams will receive the AP Seminar and Research Certificate. </t>
   </si>
   <si>
     <t>Drama 1</t>
@@ -856,6 +859,9 @@
     <t>Successful completion of Biology</t>
   </si>
   <si>
+    <t>Life Science</t>
+  </si>
+  <si>
     <t>Students will study natural and chemical functions of the body and will be prepared for further work in fields related to health careers. Topics for study will include the major systems of the body-digestive, circulatory, nervous, reproductive. Individual projects/laboratory work will be emphasized. Students will conduct animal and organ dissections.</t>
   </si>
   <si>
@@ -1075,9 +1081,6 @@
     <t>SAI U.S. History</t>
   </si>
   <si>
-    <t>U.S. History</t>
-  </si>
-  <si>
     <t>Students receive instruction that parallels the standard U.S. History program. Accommodated instruction covers U.S. political, social, and economic history from the Colonial period through contemporary times.</t>
   </si>
   <si>
@@ -1252,9 +1255,6 @@
     <t>SAI US History APD</t>
   </si>
   <si>
-    <t>History</t>
-  </si>
-  <si>
     <t>Students receive instruction that parallels the regular U.S. History program.  Modified instruction covers U.S. political, social, and economic history from the Colonial period through contemporary times.</t>
   </si>
   <si>
@@ -1282,6 +1282,9 @@
     <t>SAI Algebra APD</t>
   </si>
   <si>
+    <t xml:space="preserve">The course includes opportunities in modified computation, math facts, and numbers sense, integrating Algebra and Geometry concepts. Students work on problem solving techniques and real life modeling in practical applications. </t>
+  </si>
+  <si>
     <t>716603S</t>
   </si>
   <si>
@@ -1357,7 +1360,7 @@
     <t>This is a college-level class. An in-depth exposure to computer hardware and operating systems. Students learn the functionality of hardware and software components as well as suggested best practices in maintenance and safety issues. Through hands-on activities and labs, students learn how to assemble and configure a computer, install operating systems and software, and troubleshoot problems. An introduction to computer networking is included.</t>
   </si>
   <si>
-    <t>This course is a specialization-level course designed to follow the Project Lead the Way Engineering foundation courses.</t>
+    <t>This is a college-level class. Interested in a career involving children?  Considering a career as a pediatrician, teacher, psychologist, or social worker?  If so, the Developmental Psychology of Children (DPOC) course is for you.  DPOC is a course that combines classroom instruction and off-campus internships.  That means you learn about the development of children, while you actually get to work with them!  Internships take place during the scheduled class time at local elementary schools, child care centers, or preschools.  Opportunities for after-school paid internships are also available.  Throughout the school year, you will study a variety of child growth and development topics, and you will learn how to work with children ages birth to adolescence.  In addition, you will be trained in CPR.  After successfully completing the course, you are eligible to receive transferable college credits (for free) from Las Positas College!  Make a difference in a child’s life… enroll in Developmental Psychology of Children.  Internship is a required component of the program. Proof of a current TB Test provided by the student to work in the community. Students in after-school paid internships Students in Co-op may earn up to five additional credits per high school semester.</t>
   </si>
   <si>
     <t>ROP Introduction to Health Careers</t>
@@ -1435,6 +1438,9 @@
     <t>Drawing 1</t>
   </si>
   <si>
+    <t>In this hands-on course, students discover the laws of perspective, learn how to judge proportions and create an illusion of three-dimensional space with realistic shading.  Students also learn to draw the human portrait, and to mix colors and use them expressively. This is an entry level course, no prior experience is necessary, yet the advanced artists will also be challenged to learn new skills and techniques.  Each sequential step of the curriculum is designed to build confidence and lay the foundation for self-expression. Knowing how to draw is no less than learning how to see and that is the fundamental knowledge underlying all the visual arts. This is a great course to prepare students for future studies in fine and applied arts, including electronic media.  Students also learn about famous artists and how art influences culture and history.</t>
+  </si>
+  <si>
     <t>Honors Artist Portfolio (HP)</t>
   </si>
   <si>
@@ -1708,7 +1714,7 @@
     <t>AP French Language and Culture (HP)</t>
   </si>
   <si>
-    <t>literature will be read and discussed. Advanced concepts in grammar, writing and speaking are taught.  Culture is also explored.  This class is taught exclusively in the target language. Work outside of class : 30 minutes per day, 5 days per week, plus additional time for test preparation. This course is comparable to a 3rd year college-level course.  It consists of a thorough review of all the major French grammatical structures, reading and discussion of literature in French, in-depth discussion of news and current events, essay writing, practice in speaking, and frequent tests. It culminates in the taking of the Advanced Placement exam in French language. Students who pass the exam may receive college credit. This class is taught exclusively in the target language. Work outside of class: 30 minutes per day, 5 days per week, plus additional time for test preparation.</t>
+    <t>This course is comparable to a 3rd year college-level course.  It consists of a thorough review of all the major French grammatical structures, reading and discussion of literature in French, in-depth discussion of news and current events, essay writing, practice in speaking, and frequent tests. It culminates in the taking of the Advanced Placement exam in French language. Students who pass the exam may receive college credit. This class is taught exclusively in the target language.</t>
   </si>
   <si>
     <t>Korean 1</t>
@@ -2211,22 +2217,22 @@
         <v>26</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>19</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
@@ -2234,7 +2240,7 @@
         <v>717019.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" s="1">
         <v>10.0</v>
@@ -2243,10 +2249,10 @@
         <v>15</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>18</v>
@@ -2255,7 +2261,7 @@
         <v>19</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>35</v>
@@ -2264,7 +2270,7 @@
         <v>18</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>26</v>
@@ -2290,7 +2296,7 @@
         <v>38</v>
       </c>
       <c r="F5" s="1">
-        <v>717015.0</v>
+        <v>717010.0</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>18</v>
@@ -2299,7 +2305,7 @@
         <v>19</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>39</v>
@@ -2343,7 +2349,7 @@
         <v>26</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>42</v>
@@ -2387,7 +2393,7 @@
         <v>19</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>47</v>
@@ -2431,7 +2437,7 @@
         <v>19</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>52</v>
@@ -2440,7 +2446,7 @@
         <v>43</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>26</v>
@@ -2651,13 +2657,13 @@
         <v>26</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>64</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L13" s="1" t="s">
         <v>44</v>
@@ -2695,7 +2701,7 @@
         <v>19</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>68</v>
@@ -2739,13 +2745,13 @@
         <v>19</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>72</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L15" s="1">
         <v>12.0</v>
@@ -2915,7 +2921,7 @@
         <v>26</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>86</v>
@@ -3012,7 +3018,7 @@
         <v>22</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>26</v>
@@ -3047,13 +3053,13 @@
         <v>26</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>34</v>
+        <v>93</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L22" s="1">
         <v>9.0</v>
@@ -3070,7 +3076,7 @@
         <v>753353.0</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C23" s="1">
         <v>5.0</v>
@@ -3094,7 +3100,7 @@
         <v>55</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K23" s="1" t="s">
         <v>22</v>
@@ -3114,7 +3120,7 @@
         <v>753361.0</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C24" s="1">
         <v>5.0</v>
@@ -3123,7 +3129,7 @@
         <v>81</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F24" s="1">
         <v>753681.0</v>
@@ -3138,7 +3144,7 @@
         <v>55</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K24" s="1" t="s">
         <v>22</v>
@@ -3158,7 +3164,7 @@
         <v>753387.0</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C25" s="1">
         <v>5.0</v>
@@ -3167,7 +3173,7 @@
         <v>81</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F25" s="1">
         <v>753681.0</v>
@@ -3182,7 +3188,7 @@
         <v>55</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K25" s="1" t="s">
         <v>22</v>
@@ -3202,7 +3208,7 @@
         <v>753390.0</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C26" s="1">
         <v>5.0</v>
@@ -3226,7 +3232,7 @@
         <v>55</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K26" s="1" t="s">
         <v>22</v>
@@ -3246,7 +3252,7 @@
         <v>753332.0</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C27" s="1">
         <v>5.0</v>
@@ -3270,7 +3276,7 @@
         <v>55</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K27" s="1" t="s">
         <v>22</v>
@@ -3290,7 +3296,7 @@
         <v>753710.0</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C28" s="1">
         <v>10.0</v>
@@ -3314,7 +3320,7 @@
         <v>55</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K28" s="1" t="s">
         <v>79</v>
@@ -3334,7 +3340,7 @@
         <v>754000.0</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C29" s="1">
         <v>10.0</v>
@@ -3343,7 +3349,7 @@
         <v>15</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>18</v>
@@ -3358,7 +3364,7 @@
         <v>55</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K29" s="1" t="s">
         <v>22</v>
@@ -3378,7 +3384,7 @@
         <v>753391.0</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C30" s="1">
         <v>10.0</v>
@@ -3402,7 +3408,7 @@
         <v>55</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>22</v>
@@ -3422,7 +3428,7 @@
         <v>753351.0</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C31" s="1">
         <v>5.0</v>
@@ -3446,7 +3452,7 @@
         <v>55</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K31" s="1" t="s">
         <v>22</v>
@@ -3466,7 +3472,7 @@
         <v>753715.0</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C32" s="1">
         <v>10.0</v>
@@ -3490,7 +3496,7 @@
         <v>55</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K32" s="1" t="s">
         <v>22</v>
@@ -3510,7 +3516,7 @@
         <v>753389.0</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C33" s="1">
         <v>5.0</v>
@@ -3534,7 +3540,7 @@
         <v>55</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K33" s="1" t="s">
         <v>22</v>
@@ -3554,7 +3560,7 @@
         <v>776004.0</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C34" s="1">
         <v>10.0</v>
@@ -3575,13 +3581,13 @@
         <v>26</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L34" s="1" t="s">
         <v>44</v>
@@ -3598,7 +3604,7 @@
         <v>714802.0</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C35" s="1">
         <v>5.0</v>
@@ -3619,13 +3625,13 @@
         <v>26</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L35" s="1" t="s">
         <v>49</v>
@@ -3642,7 +3648,7 @@
         <v>714838.0</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C36" s="1">
         <v>10.0</v>
@@ -3669,7 +3675,7 @@
         <v>128</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L36" s="1">
         <v>10.0</v>
@@ -3751,13 +3757,13 @@
         <v>26</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L38" s="1">
         <v>11.0</v>
@@ -3774,7 +3780,7 @@
         <v>714822.0</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C39" s="1">
         <v>10.0</v>
@@ -3795,10 +3801,10 @@
         <v>19</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K39" s="1" t="s">
         <v>18</v>
@@ -3818,7 +3824,7 @@
         <v>714828.0</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C40" s="1">
         <v>5.0</v>
@@ -3839,13 +3845,13 @@
         <v>19</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L40" s="1">
         <v>12.0</v>
@@ -3862,7 +3868,7 @@
         <v>717240.0</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C41" s="1">
         <v>10.0</v>
@@ -3883,10 +3889,10 @@
         <v>19</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K41" s="1" t="s">
         <v>18</v>
@@ -3906,7 +3912,7 @@
         <v>714823.0</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C42" s="1">
         <v>5.0</v>
@@ -3927,10 +3933,10 @@
         <v>26</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K42" s="1" t="s">
         <v>131</v>
@@ -3950,7 +3956,7 @@
         <v>714827.0</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C43" s="1">
         <v>5.0</v>
@@ -3971,10 +3977,10 @@
         <v>19</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K43" s="1" t="s">
         <v>131</v>
@@ -3994,7 +4000,7 @@
         <v>714829.0</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C44" s="1">
         <v>5.0</v>
@@ -4015,10 +4021,10 @@
         <v>19</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K44" s="1" t="s">
         <v>131</v>
@@ -4038,7 +4044,7 @@
         <v>714826.0</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C45" s="1">
         <v>5.0</v>
@@ -4059,13 +4065,13 @@
         <v>26</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L45" s="1">
         <v>12.0</v>
@@ -4082,7 +4088,7 @@
         <v>714805.0</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C46" s="1">
         <v>5.0</v>
@@ -4103,13 +4109,13 @@
         <v>26</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L46" s="1" t="s">
         <v>49</v>
@@ -4126,7 +4132,7 @@
         <v>717242.0</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C47" s="1">
         <v>5.0</v>
@@ -4147,16 +4153,16 @@
         <v>26</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M47" s="1" t="s">
         <v>26</v>
@@ -4170,7 +4176,7 @@
         <v>717241.0</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C48" s="1">
         <v>5.0</v>
@@ -4179,7 +4185,7 @@
         <v>81</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F48" s="1">
         <v>797060.0</v>
@@ -4191,13 +4197,13 @@
         <v>26</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L48" s="1" t="s">
         <v>49</v>
@@ -4214,7 +4220,7 @@
         <v>797060.0</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C49" s="1">
         <v>10.0</v>
@@ -4235,16 +4241,16 @@
         <v>26</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M49" s="1" t="s">
         <v>26</v>
@@ -4258,7 +4264,7 @@
         <v>797100.0</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C50" s="1">
         <v>10.0</v>
@@ -4267,7 +4273,7 @@
         <v>15</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F50" s="1">
         <v>797060.0</v>
@@ -4279,10 +4285,10 @@
         <v>26</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K50" s="1" t="s">
         <v>18</v>
@@ -4302,7 +4308,7 @@
         <v>714800.0</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C51" s="1">
         <v>10.0</v>
@@ -4323,10 +4329,10 @@
         <v>19</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K51" s="1" t="s">
         <v>131</v>
@@ -4346,7 +4352,7 @@
         <v>714832.0</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C52" s="1">
         <v>10.0</v>
@@ -4367,16 +4373,16 @@
         <v>19</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K52" s="1" t="s">
         <v>131</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M52" s="1" t="s">
         <v>26</v>
@@ -4390,7 +4396,7 @@
         <v>797251.0</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C53" s="1">
         <v>10.0</v>
@@ -4399,10 +4405,10 @@
         <v>15</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>18</v>
@@ -4411,10 +4417,10 @@
         <v>19</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K53" s="1" t="s">
         <v>131</v>
@@ -4434,7 +4440,7 @@
         <v>797252.0</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C54" s="1">
         <v>10.0</v>
@@ -4443,7 +4449,7 @@
         <v>15</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F54" s="1">
         <v>797251.0</v>
@@ -4455,16 +4461,16 @@
         <v>19</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K54" s="1" t="s">
         <v>131</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M54" s="1" t="s">
         <v>26</v>
@@ -4478,7 +4484,7 @@
         <v>797255.0</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C55" s="1">
         <v>10.0</v>
@@ -4487,10 +4493,10 @@
         <v>15</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>18</v>
@@ -4499,13 +4505,13 @@
         <v>19</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L55" s="1" t="s">
         <v>49</v>
@@ -4522,7 +4528,7 @@
         <v>720000.0</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C56" s="1">
         <v>10.0</v>
@@ -4531,7 +4537,7 @@
         <v>15</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>18</v>
@@ -4543,13 +4549,13 @@
         <v>26</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L56" s="1">
         <v>9.0</v>
@@ -4566,7 +4572,7 @@
         <v>720010.0</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C57" s="1">
         <v>10.0</v>
@@ -4575,7 +4581,7 @@
         <v>15</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F57" s="1">
         <v>720000.0</v>
@@ -4587,13 +4593,13 @@
         <v>26</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L57" s="1">
         <v>10.0</v>
@@ -4610,7 +4616,7 @@
         <v>797081.0</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C58" s="1">
         <v>10.0</v>
@@ -4619,10 +4625,10 @@
         <v>15</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>18</v>
@@ -4631,13 +4637,13 @@
         <v>26</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L58" s="1" t="s">
         <v>44</v>
@@ -4654,7 +4660,7 @@
         <v>797086.0</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C59" s="1">
         <v>10.0</v>
@@ -4663,10 +4669,10 @@
         <v>15</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>18</v>
@@ -4675,13 +4681,13 @@
         <v>26</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L59" s="1" t="s">
         <v>44</v>
@@ -4698,7 +4704,7 @@
         <v>797175.0</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C60" s="1">
         <v>10.0</v>
@@ -4707,10 +4713,10 @@
         <v>15</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>18</v>
@@ -4719,13 +4725,13 @@
         <v>26</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L60" s="1" t="s">
         <v>44</v>
@@ -4742,7 +4748,7 @@
         <v>797174.0</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C61" s="1">
         <v>10.0</v>
@@ -4751,10 +4757,10 @@
         <v>15</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>18</v>
@@ -4763,13 +4769,13 @@
         <v>19</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L61" s="1" t="s">
         <v>49</v>
@@ -4786,7 +4792,7 @@
         <v>720020.0</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C62" s="1">
         <v>10.0</v>
@@ -4795,7 +4801,7 @@
         <v>15</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F62" s="1">
         <v>720010.0</v>
@@ -4807,13 +4813,13 @@
         <v>26</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L62" s="1">
         <v>11.0</v>
@@ -4830,7 +4836,7 @@
         <v>720030.0</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C63" s="1">
         <v>10.0</v>
@@ -4839,7 +4845,7 @@
         <v>15</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F63" s="1">
         <v>720020.0</v>
@@ -4851,13 +4857,13 @@
         <v>26</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L63" s="1">
         <v>12.0</v>
@@ -4874,7 +4880,7 @@
         <v>717250.0</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C64" s="1">
         <v>10.0</v>
@@ -4895,10 +4901,10 @@
         <v>19</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K64" s="1" t="s">
         <v>18</v>
@@ -4918,7 +4924,7 @@
         <v>710414.0</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C65" s="1">
         <v>10.0</v>
@@ -4939,13 +4945,13 @@
         <v>26</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L65" s="1" t="s">
         <v>44</v>
@@ -4962,7 +4968,7 @@
         <v>710417.0</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C66" s="1">
         <v>10.0</v>
@@ -4971,7 +4977,7 @@
         <v>15</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F66" s="1">
         <v>710414.0</v>
@@ -4983,13 +4989,13 @@
         <v>26</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L66" s="1" t="s">
         <v>44</v>
@@ -5006,7 +5012,7 @@
         <v>717251.0</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C67" s="1">
         <v>10.0</v>
@@ -5015,7 +5021,7 @@
         <v>15</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F67" s="1">
         <v>717250.0</v>
@@ -5027,16 +5033,16 @@
         <v>19</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M67" s="1" t="s">
         <v>26</v>
@@ -5050,7 +5056,7 @@
         <v>717101.0</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C68" s="1">
         <v>5.0</v>
@@ -5059,7 +5065,7 @@
         <v>81</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>18</v>
@@ -5071,16 +5077,16 @@
         <v>26</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K68" s="1" t="s">
         <v>18</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M68" s="1" t="s">
         <v>26</v>
@@ -5094,37 +5100,37 @@
         <v>717100.0</v>
       </c>
       <c r="B69" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C69" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J69" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="C69" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G69" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H69" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I69" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J69" s="1" t="s">
-        <v>228</v>
-      </c>
       <c r="K69" s="1" t="s">
         <v>18</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M69" s="1" t="s">
         <v>26</v>
@@ -5138,7 +5144,7 @@
         <v>717140.0</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C70" s="1">
         <v>10.0</v>
@@ -5147,7 +5153,7 @@
         <v>15</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>18</v>
@@ -5159,10 +5165,10 @@
         <v>26</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K70" s="1" t="s">
         <v>18</v>
@@ -5182,7 +5188,7 @@
         <v>710493.0</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C71" s="1">
         <v>10.0</v>
@@ -5203,13 +5209,13 @@
         <v>26</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L71" s="1" t="s">
         <v>44</v>
@@ -5226,7 +5232,7 @@
         <v>710200.0</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C72" s="1">
         <v>10.0</v>
@@ -5235,7 +5241,7 @@
         <v>15</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F72" s="1">
         <v>710493.0</v>
@@ -5247,13 +5253,13 @@
         <v>26</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L72" s="1" t="s">
         <v>44</v>
@@ -5270,7 +5276,7 @@
         <v>710600.0</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C73" s="1">
         <v>10.0</v>
@@ -5291,13 +5297,13 @@
         <v>26</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L73" s="1" t="s">
         <v>44</v>
@@ -5314,7 +5320,7 @@
         <v>710770.0</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C74" s="1">
         <v>10.0</v>
@@ -5323,7 +5329,7 @@
         <v>15</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>18</v>
@@ -5335,13 +5341,13 @@
         <v>26</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L74" s="1" t="s">
         <v>44</v>
@@ -5358,7 +5364,7 @@
         <v>710479.0</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C75" s="1">
         <v>10.0</v>
@@ -5379,13 +5385,13 @@
         <v>26</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L75" s="1" t="s">
         <v>44</v>
@@ -5402,34 +5408,34 @@
         <v>710480.0</v>
       </c>
       <c r="B76" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C76" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="K76" s="1" t="s">
         <v>249</v>
-      </c>
-      <c r="C76" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G76" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H76" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I76" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="J76" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="K76" s="1" t="s">
-        <v>248</v>
       </c>
       <c r="L76" s="1" t="s">
         <v>44</v>
@@ -5446,7 +5452,7 @@
         <v>710481.0</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C77" s="1">
         <v>10.0</v>
@@ -5455,7 +5461,7 @@
         <v>15</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>18</v>
@@ -5467,13 +5473,13 @@
         <v>19</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L77" s="1" t="s">
         <v>44</v>
@@ -5490,7 +5496,7 @@
         <v>711280.0</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C78" s="1">
         <v>10.0</v>
@@ -5499,7 +5505,7 @@
         <v>15</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F78" s="1">
         <v>711225.0</v>
@@ -5511,10 +5517,10 @@
         <v>26</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K78" s="1" t="s">
         <v>18</v>
@@ -5534,7 +5540,7 @@
         <v>710472.0</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C79" s="1">
         <v>10.0</v>
@@ -5543,7 +5549,7 @@
         <v>15</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>18</v>
@@ -5555,13 +5561,13 @@
         <v>19</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L79" s="1" t="s">
         <v>44</v>
@@ -5578,7 +5584,7 @@
         <v>710773.0</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C80" s="1">
         <v>10.0</v>
@@ -5587,7 +5593,7 @@
         <v>15</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>18</v>
@@ -5599,13 +5605,13 @@
         <v>19</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L80" s="1" t="s">
         <v>44</v>
@@ -5622,7 +5628,7 @@
         <v>710450.0</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C81" s="1">
         <v>10.0</v>
@@ -5643,13 +5649,13 @@
         <v>26</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L81" s="1" t="s">
         <v>44</v>
@@ -5666,7 +5672,7 @@
         <v>710451.0</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C82" s="1">
         <v>10.0</v>
@@ -5687,13 +5693,13 @@
         <v>26</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L82" s="1" t="s">
         <v>44</v>
@@ -5710,7 +5716,7 @@
         <v>710407.0</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C83" s="1">
         <v>10.0</v>
@@ -5731,13 +5737,13 @@
         <v>26</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L83" s="1" t="s">
         <v>44</v>
@@ -5754,7 +5760,7 @@
         <v>710120.0</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C84" s="1">
         <v>10.0</v>
@@ -5775,13 +5781,13 @@
         <v>26</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L84" s="1" t="s">
         <v>44</v>
@@ -5798,7 +5804,7 @@
         <v>711225.0</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C85" s="1">
         <v>10.0</v>
@@ -5819,10 +5825,10 @@
         <v>26</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K85" s="1" t="s">
         <v>18</v>
@@ -5842,7 +5848,7 @@
         <v>711282.0</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C86" s="1">
         <v>5.0</v>
@@ -5851,7 +5857,7 @@
         <v>81</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F86" s="1">
         <v>711225.0</v>
@@ -5863,10 +5869,10 @@
         <v>26</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K86" s="1" t="s">
         <v>18</v>
@@ -5886,7 +5892,7 @@
         <v>711265.0</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C87" s="1">
         <v>10.0</v>
@@ -5895,7 +5901,7 @@
         <v>15</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F87" s="1">
         <v>711225.0</v>
@@ -5907,13 +5913,13 @@
         <v>26</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L87" s="1" t="s">
         <v>49</v>
@@ -5930,7 +5936,7 @@
         <v>713780.0</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C88" s="1">
         <v>10.0</v>
@@ -5939,7 +5945,7 @@
         <v>15</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F88" s="1">
         <v>713760.0</v>
@@ -5951,16 +5957,16 @@
         <v>26</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>20</v>
+        <v>282</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M88" s="1" t="s">
         <v>26</v>
@@ -5974,7 +5980,7 @@
         <v>713742.0</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C89" s="1">
         <v>10.0</v>
@@ -5983,7 +5989,7 @@
         <v>15</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F89" s="1">
         <v>713760.0</v>
@@ -5995,13 +6001,13 @@
         <v>26</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J89" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="L89" s="1" t="s">
         <v>49</v>
@@ -6018,7 +6024,7 @@
         <v>713735.0</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C90" s="1">
         <v>10.0</v>
@@ -6027,7 +6033,7 @@
         <v>15</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F90" s="1">
         <v>713760.0</v>
@@ -6039,16 +6045,16 @@
         <v>26</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J90" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M90" s="1" t="s">
         <v>26</v>
@@ -6062,7 +6068,7 @@
         <v>713784.0</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C91" s="1">
         <v>10.0</v>
@@ -6071,7 +6077,7 @@
         <v>15</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F91" s="1">
         <v>797060.0</v>
@@ -6083,13 +6089,13 @@
         <v>26</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L91" s="1" t="s">
         <v>49</v>
@@ -6106,7 +6112,7 @@
         <v>711249.0</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C92" s="1">
         <v>10.0</v>
@@ -6115,7 +6121,7 @@
         <v>15</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F92" s="1">
         <v>711225.0</v>
@@ -6127,10 +6133,10 @@
         <v>26</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="K92" s="1" t="s">
         <v>18</v>
@@ -6150,7 +6156,7 @@
         <v>711226.0</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C93" s="1">
         <v>10.0</v>
@@ -6159,7 +6165,7 @@
         <v>15</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F93" s="1">
         <v>711225.0</v>
@@ -6171,10 +6177,10 @@
         <v>26</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K93" s="1" t="s">
         <v>18</v>
@@ -6194,7 +6200,7 @@
         <v>713760.0</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C94" s="1">
         <v>10.0</v>
@@ -6215,13 +6221,13 @@
         <v>26</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>20</v>
+        <v>282</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="L94" s="1" t="s">
         <v>44</v>
@@ -6238,7 +6244,7 @@
         <v>713725.0</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C95" s="1">
         <v>10.0</v>
@@ -6247,7 +6253,7 @@
         <v>15</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F95" s="1">
         <v>713760.0</v>
@@ -6259,16 +6265,16 @@
         <v>26</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M95" s="1" t="s">
         <v>26</v>
@@ -6282,7 +6288,7 @@
         <v>713727.0</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C96" s="1">
         <v>5.0</v>
@@ -6291,7 +6297,7 @@
         <v>81</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F96" s="1">
         <v>713760.0</v>
@@ -6303,16 +6309,16 @@
         <v>26</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="K96" s="1" t="s">
         <v>18</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M96" s="1" t="s">
         <v>26</v>
@@ -6326,7 +6332,7 @@
         <v>713757.0</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C97" s="1">
         <v>10.0</v>
@@ -6335,10 +6341,10 @@
         <v>15</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="G97" s="1" t="s">
         <v>18</v>
@@ -6347,16 +6353,16 @@
         <v>19</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>20</v>
+        <v>282</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M97" s="1" t="s">
         <v>26</v>
@@ -6370,7 +6376,7 @@
         <v>713788.0</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C98" s="1">
         <v>10.0</v>
@@ -6379,7 +6385,7 @@
         <v>15</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>18</v>
@@ -6391,16 +6397,16 @@
         <v>19</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>20</v>
+        <v>282</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M98" s="1" t="s">
         <v>26</v>
@@ -6414,7 +6420,7 @@
         <v>713766.0</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C99" s="1">
         <v>10.0</v>
@@ -6423,10 +6429,10 @@
         <v>15</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G99" s="1">
         <v>797100.0</v>
@@ -6435,13 +6441,13 @@
         <v>26</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L99" s="1" t="s">
         <v>49</v>
@@ -6458,7 +6464,7 @@
         <v>713767.0</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C100" s="1">
         <v>10.0</v>
@@ -6467,10 +6473,10 @@
         <v>15</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G100" s="1">
         <v>797100.0</v>
@@ -6479,13 +6485,13 @@
         <v>19</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J100" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="K100" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="K100" s="1" t="s">
-        <v>320</v>
       </c>
       <c r="L100" s="1" t="s">
         <v>49</v>
@@ -6502,7 +6508,7 @@
         <v>713776.0</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C101" s="1">
         <v>10.0</v>
@@ -6511,28 +6517,28 @@
         <v>15</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="H101" s="1" t="s">
         <v>19</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K101" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M101" s="1" t="s">
         <v>26</v>
@@ -6546,7 +6552,7 @@
         <v>713764.0</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C102" s="1">
         <v>10.0</v>
@@ -6555,10 +6561,10 @@
         <v>15</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G102" s="1" t="s">
         <v>18</v>
@@ -6567,13 +6573,13 @@
         <v>19</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K102" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="L102" s="1" t="s">
         <v>49</v>
@@ -6590,7 +6596,7 @@
         <v>713771.0</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C103" s="1">
         <v>10.0</v>
@@ -6599,10 +6605,10 @@
         <v>15</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G103" s="1">
         <v>797251.0</v>
@@ -6611,16 +6617,16 @@
         <v>19</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J103" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="K103" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M103" s="1" t="s">
         <v>26</v>
@@ -6634,7 +6640,7 @@
         <v>713733.0</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C104" s="1">
         <v>10.0</v>
@@ -6643,7 +6649,7 @@
         <v>15</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>18</v>
@@ -6655,10 +6661,10 @@
         <v>26</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J104" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K104" s="1" t="s">
         <v>18</v>
@@ -6678,7 +6684,7 @@
         <v>716607.0</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C105" s="1">
         <v>10.0</v>
@@ -6699,16 +6705,16 @@
         <v>26</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J105" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M105" s="1" t="s">
         <v>26</v>
@@ -6722,7 +6728,7 @@
         <v>716604.0</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C106" s="1">
         <v>10.0</v>
@@ -6743,13 +6749,13 @@
         <v>26</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>20</v>
+        <v>282</v>
       </c>
       <c r="J106" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="K106" s="1" t="s">
         <v>345</v>
-      </c>
-      <c r="K106" s="1" t="s">
-        <v>343</v>
       </c>
       <c r="L106" s="1" t="s">
         <v>44</v>
@@ -6766,7 +6772,7 @@
         <v>716208.0</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C107" s="1">
         <v>10.0</v>
@@ -6787,13 +6793,13 @@
         <v>26</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J107" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="L107" s="1" t="s">
         <v>49</v>
@@ -6810,7 +6816,7 @@
         <v>716609.0</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C108" s="1">
         <v>10.0</v>
@@ -6819,7 +6825,7 @@
         <v>15</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>18</v>
@@ -6831,13 +6837,13 @@
         <v>26</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J108" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K108" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L108" s="1" t="s">
         <v>49</v>
@@ -6854,7 +6860,7 @@
         <v>716608.0</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C109" s="1">
         <v>10.0</v>
@@ -6863,7 +6869,7 @@
         <v>15</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>18</v>
@@ -6875,13 +6881,13 @@
         <v>26</v>
       </c>
       <c r="I109" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="J109" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="K109" s="1" t="s">
         <v>354</v>
-      </c>
-      <c r="J109" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="K109" s="1" t="s">
-        <v>352</v>
       </c>
       <c r="L109" s="1">
         <v>12.0</v>
@@ -6898,7 +6904,7 @@
         <v>716605.0</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C110" s="1">
         <v>5.0</v>
@@ -6907,7 +6913,7 @@
         <v>81</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>18</v>
@@ -6919,13 +6925,13 @@
         <v>26</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="J110" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L110" s="1">
         <v>10.0</v>
@@ -6942,7 +6948,7 @@
         <v>716602.0</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C111" s="1">
         <v>10.0</v>
@@ -6951,7 +6957,7 @@
         <v>15</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>18</v>
@@ -6963,13 +6969,13 @@
         <v>26</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>20</v>
+        <v>282</v>
       </c>
       <c r="J111" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L111" s="1" t="s">
         <v>44</v>
@@ -6986,7 +6992,7 @@
         <v>716611.0</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C112" s="1">
         <v>10.0</v>
@@ -6995,7 +7001,7 @@
         <v>15</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>18</v>
@@ -7010,13 +7016,13 @@
         <v>55</v>
       </c>
       <c r="J112" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M112" s="1" t="s">
         <v>26</v>
@@ -7030,7 +7036,7 @@
         <v>716612.0</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C113" s="1">
         <v>10.0</v>
@@ -7039,7 +7045,7 @@
         <v>15</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>18</v>
@@ -7054,10 +7060,10 @@
         <v>55</v>
       </c>
       <c r="J113" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L113" s="3">
         <v>46307.0</v>
@@ -7074,7 +7080,7 @@
         <v>716600.0</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C114" s="1">
         <v>10.0</v>
@@ -7083,7 +7089,7 @@
         <v>15</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>18</v>
@@ -7095,13 +7101,13 @@
         <v>26</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J114" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K114" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L114" s="1" t="s">
         <v>44</v>
@@ -7118,34 +7124,34 @@
         <v>716601.0</v>
       </c>
       <c r="B115" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C115" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I115" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="J115" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="K115" s="1" t="s">
         <v>368</v>
-      </c>
-      <c r="C115" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="F115" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G115" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H115" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I115" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="J115" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="K115" s="1" t="s">
-        <v>367</v>
       </c>
       <c r="L115" s="1" t="s">
         <v>44</v>
@@ -7162,7 +7168,7 @@
         <v>713785.0</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C116" s="1">
         <v>10.0</v>
@@ -7171,7 +7177,7 @@
         <v>15</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F116" s="1">
         <v>713760.0</v>
@@ -7183,13 +7189,13 @@
         <v>26</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>20</v>
+        <v>282</v>
       </c>
       <c r="J116" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K116" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L116" s="1" t="s">
         <v>49</v>
@@ -7206,7 +7212,7 @@
         <v>713737.0</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C117" s="1">
         <v>10.0</v>
@@ -7215,10 +7221,10 @@
         <v>15</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G117" s="1" t="s">
         <v>18</v>
@@ -7227,10 +7233,10 @@
         <v>19</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J117" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K117" s="1" t="s">
         <v>131</v>
@@ -7250,7 +7256,7 @@
         <v>713736.0</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C118" s="1">
         <v>10.0</v>
@@ -7259,7 +7265,7 @@
         <v>15</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F118" s="1">
         <v>713785.0</v>
@@ -7271,16 +7277,16 @@
         <v>19</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>20</v>
+        <v>282</v>
       </c>
       <c r="J118" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M118" s="1" t="s">
         <v>26</v>
@@ -7291,10 +7297,10 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C119" s="1">
         <v>10.0</v>
@@ -7303,7 +7309,7 @@
         <v>15</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>18</v>
@@ -7315,10 +7321,10 @@
         <v>26</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J119" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="K119" s="1" t="s">
         <v>18</v>
@@ -7335,10 +7341,10 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C120" s="1">
         <v>10.0</v>
@@ -7347,7 +7353,7 @@
         <v>15</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>18</v>
@@ -7359,10 +7365,10 @@
         <v>26</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>20</v>
+        <v>282</v>
       </c>
       <c r="J120" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K120" s="1" t="s">
         <v>18</v>
@@ -7379,10 +7385,10 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C121" s="1">
         <v>10.0</v>
@@ -7391,7 +7397,7 @@
         <v>15</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>18</v>
@@ -7403,10 +7409,10 @@
         <v>26</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J121" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K121" s="1" t="s">
         <v>18</v>
@@ -7423,10 +7429,10 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C122" s="1">
         <v>10.0</v>
@@ -7447,13 +7453,13 @@
         <v>26</v>
       </c>
       <c r="I122" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J122" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="K122" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L122" s="1">
         <v>12.0</v>
@@ -7467,10 +7473,10 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C123" s="1">
         <v>10.0</v>
@@ -7491,13 +7497,13 @@
         <v>26</v>
       </c>
       <c r="I123" s="1" t="s">
-        <v>20</v>
+        <v>282</v>
       </c>
       <c r="J123" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="K123" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L123" s="4">
         <v>41162.0</v>
@@ -7514,7 +7520,7 @@
         <v>716150.0</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C124" s="1">
         <v>10.0</v>
@@ -7535,13 +7541,13 @@
         <v>26</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J124" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K124" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L124" s="1">
         <v>12.0</v>
@@ -7555,10 +7561,10 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C125" s="1">
         <v>10.0</v>
@@ -7579,10 +7585,10 @@
         <v>26</v>
       </c>
       <c r="I125" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J125" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="K125" s="1" t="s">
         <v>18</v>
@@ -7599,10 +7605,10 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C126" s="1">
         <v>10.0</v>
@@ -7626,10 +7632,10 @@
         <v>55</v>
       </c>
       <c r="J126" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K126" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L126" s="1" t="s">
         <v>44</v>
@@ -7643,37 +7649,37 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C127" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H127" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I127" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="J127" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="K127" s="1" t="s">
         <v>405</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="C127" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F127" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G127" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H127" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I127" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="J127" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="K127" s="1" t="s">
-        <v>404</v>
       </c>
       <c r="L127" s="4">
         <v>41162.0</v>
@@ -7687,10 +7693,10 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C128" s="1">
         <v>10.0</v>
@@ -7711,13 +7717,13 @@
         <v>26</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J128" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="K128" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="L128" s="3">
         <v>46307.0</v>
@@ -7731,10 +7737,10 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C129" s="1">
         <v>10.0</v>
@@ -7743,7 +7749,7 @@
         <v>15</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>18</v>
@@ -7755,7 +7761,7 @@
         <v>26</v>
       </c>
       <c r="I129" s="1" t="s">
-        <v>413</v>
+        <v>133</v>
       </c>
       <c r="J129" s="1" t="s">
         <v>414</v>
@@ -7787,7 +7793,7 @@
         <v>15</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>18</v>
@@ -7799,7 +7805,7 @@
         <v>26</v>
       </c>
       <c r="I130" s="1" t="s">
-        <v>413</v>
+        <v>127</v>
       </c>
       <c r="J130" s="1" t="s">
         <v>417</v>
@@ -7831,7 +7837,7 @@
         <v>15</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>18</v>
@@ -7843,7 +7849,7 @@
         <v>26</v>
       </c>
       <c r="I131" s="1" t="s">
-        <v>413</v>
+        <v>138</v>
       </c>
       <c r="J131" s="1" t="s">
         <v>420</v>
@@ -7875,7 +7881,7 @@
         <v>15</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>18</v>
@@ -7887,10 +7893,10 @@
         <v>26</v>
       </c>
       <c r="I132" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J132" s="1" t="s">
-        <v>18</v>
+        <v>423</v>
       </c>
       <c r="K132" s="1" t="s">
         <v>18</v>
@@ -7907,10 +7913,10 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C133" s="1">
         <v>5.0</v>
@@ -7919,7 +7925,7 @@
         <v>81</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>18</v>
@@ -7931,13 +7937,13 @@
         <v>26</v>
       </c>
       <c r="I133" s="1" t="s">
-        <v>413</v>
+        <v>138</v>
       </c>
       <c r="J133" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K133" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L133" s="1">
         <v>12.0</v>
@@ -7951,10 +7957,10 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C134" s="1">
         <v>5.0</v>
@@ -7963,7 +7969,7 @@
         <v>81</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>18</v>
@@ -7975,13 +7981,13 @@
         <v>26</v>
       </c>
       <c r="I134" s="1" t="s">
-        <v>413</v>
+        <v>138</v>
       </c>
       <c r="J134" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K134" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L134" s="1">
         <v>12.0</v>
@@ -7995,10 +8001,10 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C135" s="1">
         <v>10.0</v>
@@ -8007,7 +8013,7 @@
         <v>15</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>18</v>
@@ -8019,16 +8025,16 @@
         <v>26</v>
       </c>
       <c r="I135" s="1" t="s">
-        <v>413</v>
+        <v>133</v>
       </c>
       <c r="J135" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="K135" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M135" s="1" t="s">
         <v>26</v>
@@ -8039,10 +8045,10 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C136" s="1">
         <v>10.0</v>
@@ -8051,7 +8057,7 @@
         <v>15</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>18</v>
@@ -8063,13 +8069,13 @@
         <v>26</v>
       </c>
       <c r="I136" s="1" t="s">
-        <v>20</v>
+        <v>282</v>
       </c>
       <c r="J136" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K136" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L136" s="1">
         <v>12.0</v>
@@ -8086,7 +8092,7 @@
         <v>715179.0</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C137" s="1">
         <v>10.0</v>
@@ -8107,22 +8113,22 @@
         <v>26</v>
       </c>
       <c r="I137" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J137" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="K137" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M137" s="1" t="s">
         <v>19</v>
       </c>
       <c r="N137" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="138">
@@ -8130,7 +8136,7 @@
         <v>715178.0</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C138" s="1">
         <v>10.0</v>
@@ -8151,22 +8157,22 @@
         <v>26</v>
       </c>
       <c r="I138" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J138" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K138" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L138" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M138" s="1" t="s">
         <v>19</v>
       </c>
       <c r="N138" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="139">
@@ -8174,7 +8180,7 @@
         <v>715118.0</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C139" s="1">
         <v>10.0</v>
@@ -8183,7 +8189,7 @@
         <v>15</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F139" s="1">
         <v>715117.0</v>
@@ -8195,22 +8201,22 @@
         <v>26</v>
       </c>
       <c r="I139" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J139" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K139" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L139" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M139" s="1" t="s">
         <v>19</v>
       </c>
       <c r="N139" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="140">
@@ -8218,13 +8224,13 @@
         <v>715190.0</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C140" s="1">
         <v>5.0</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>18</v>
@@ -8239,10 +8245,10 @@
         <v>26</v>
       </c>
       <c r="I140" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J140" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="K140" s="1" t="s">
         <v>22</v>
@@ -8254,7 +8260,7 @@
         <v>19</v>
       </c>
       <c r="N140" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="141">
@@ -8262,7 +8268,7 @@
         <v>715170.0</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C141" s="1">
         <v>10.0</v>
@@ -8283,22 +8289,22 @@
         <v>26</v>
       </c>
       <c r="I141" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J141" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K141" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L141" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M141" s="1" t="s">
         <v>19</v>
       </c>
       <c r="N141" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="142">
@@ -8306,7 +8312,7 @@
         <v>715236.0</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C142" s="1">
         <v>10.0</v>
@@ -8327,16 +8333,16 @@
         <v>26</v>
       </c>
       <c r="I142" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J142" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K142" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L142" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M142" s="1" t="s">
         <v>19</v>
@@ -8350,7 +8356,7 @@
         <v>715117.0</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C143" s="1">
         <v>10.0</v>
@@ -8371,22 +8377,22 @@
         <v>26</v>
       </c>
       <c r="I143" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J143" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K143" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L143" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M143" s="1" t="s">
         <v>19</v>
       </c>
       <c r="N143" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="144">
@@ -8394,7 +8400,7 @@
         <v>715195.0</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C144" s="1">
         <v>10.0</v>
@@ -8415,10 +8421,10 @@
         <v>26</v>
       </c>
       <c r="I144" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J144" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K144" s="1" t="s">
         <v>22</v>
@@ -8430,7 +8436,7 @@
         <v>19</v>
       </c>
       <c r="N144" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="145">
@@ -8438,7 +8444,7 @@
         <v>715194.0</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C145" s="1">
         <v>10.0</v>
@@ -8459,13 +8465,13 @@
         <v>26</v>
       </c>
       <c r="I145" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J145" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K145" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L145" s="1" t="s">
         <v>49</v>
@@ -8474,7 +8480,7 @@
         <v>19</v>
       </c>
       <c r="N145" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="146">
@@ -8482,7 +8488,7 @@
         <v>715200.0</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C146" s="1">
         <v>10.0</v>
@@ -8491,7 +8497,7 @@
         <v>15</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F146" s="1">
         <v>715194.0</v>
@@ -8503,22 +8509,22 @@
         <v>26</v>
       </c>
       <c r="I146" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J146" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="K146" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L146" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M146" s="1" t="s">
         <v>19</v>
       </c>
       <c r="N146" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="147">
@@ -8526,7 +8532,7 @@
         <v>715101.0</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C147" s="1">
         <v>10.0</v>
@@ -8547,16 +8553,16 @@
         <v>26</v>
       </c>
       <c r="I147" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J147" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="K147" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L147" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M147" s="1" t="s">
         <v>19</v>
@@ -8570,7 +8576,7 @@
         <v>715103.0</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C148" s="1">
         <v>10.0</v>
@@ -8591,16 +8597,16 @@
         <v>26</v>
       </c>
       <c r="I148" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J148" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="K148" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L148" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M148" s="1" t="s">
         <v>19</v>
@@ -8614,7 +8620,7 @@
         <v>715104.0</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C149" s="1">
         <v>10.0</v>
@@ -8635,22 +8641,22 @@
         <v>26</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J149" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="K149" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L149" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M149" s="1" t="s">
         <v>19</v>
       </c>
       <c r="N149" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="150">
@@ -8658,7 +8664,7 @@
         <v>715106.0</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C150" s="1">
         <v>10.0</v>
@@ -8670,7 +8676,7 @@
         <v>18</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G150" s="1" t="s">
         <v>18</v>
@@ -8679,22 +8685,22 @@
         <v>26</v>
       </c>
       <c r="I150" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J150" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="K150" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L150" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M150" s="1" t="s">
         <v>19</v>
       </c>
       <c r="N150" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="151">
@@ -8702,7 +8708,7 @@
         <v>715188.0</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C151" s="1">
         <v>10.0</v>
@@ -8711,7 +8717,7 @@
         <v>15</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>18</v>
@@ -8723,22 +8729,22 @@
         <v>26</v>
       </c>
       <c r="I151" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J151" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K151" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L151" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M151" s="1" t="s">
         <v>19</v>
       </c>
       <c r="N151" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="152">
@@ -8746,7 +8752,7 @@
         <v>715189.0</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C152" s="1">
         <v>10.0</v>
@@ -8755,7 +8761,7 @@
         <v>15</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>18</v>
@@ -8767,22 +8773,22 @@
         <v>26</v>
       </c>
       <c r="I152" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J152" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="K152" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L152" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M152" s="1" t="s">
         <v>19</v>
       </c>
       <c r="N152" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="153">
@@ -8790,7 +8796,7 @@
         <v>724000.0</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C153" s="1">
         <v>10.0</v>
@@ -8811,10 +8817,10 @@
         <v>26</v>
       </c>
       <c r="I153" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J153" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K153" s="1" t="s">
         <v>18</v>
@@ -8834,7 +8840,7 @@
         <v>715800.0</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C154" s="1">
         <v>10.0</v>
@@ -8843,7 +8849,7 @@
         <v>15</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>18</v>
@@ -8855,16 +8861,16 @@
         <v>19</v>
       </c>
       <c r="I154" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J154" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="K154" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="L154" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M154" s="1" t="s">
         <v>26</v>
@@ -8878,7 +8884,7 @@
         <v>724220.0</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C155" s="1">
         <v>10.0</v>
@@ -8887,7 +8893,7 @@
         <v>15</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>18</v>
@@ -8899,10 +8905,10 @@
         <v>19</v>
       </c>
       <c r="I155" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J155" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="K155" s="1" t="s">
         <v>18</v>
@@ -8922,7 +8928,7 @@
         <v>753331.0</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C156" s="1">
         <v>10.0</v>
@@ -8943,10 +8949,10 @@
         <v>26</v>
       </c>
       <c r="I156" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J156" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="K156" s="1" t="s">
         <v>22</v>
@@ -8966,7 +8972,7 @@
         <v>753333.0</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C157" s="1">
         <v>10.0</v>
@@ -8975,7 +8981,7 @@
         <v>15</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="F157" s="1">
         <v>753331.0</v>
@@ -8987,10 +8993,10 @@
         <v>19</v>
       </c>
       <c r="I157" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J157" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="K157" s="1" t="s">
         <v>22</v>
@@ -9010,7 +9016,7 @@
         <v>724200.0</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C158" s="1">
         <v>10.0</v>
@@ -9031,13 +9037,13 @@
         <v>26</v>
       </c>
       <c r="I158" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J158" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K158" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="L158" s="1" t="s">
         <v>44</v>
@@ -9054,7 +9060,7 @@
         <v>724600.0</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C159" s="1">
         <v>10.0</v>
@@ -9075,13 +9081,13 @@
         <v>26</v>
       </c>
       <c r="I159" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J159" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="K159" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="L159" s="1" t="s">
         <v>44</v>
@@ -9098,7 +9104,7 @@
         <v>715237.0</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C160" s="1">
         <v>10.0</v>
@@ -9119,16 +9125,16 @@
         <v>26</v>
       </c>
       <c r="I160" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J160" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="K160" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L160" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M160" s="1" t="s">
         <v>19</v>
@@ -9142,16 +9148,16 @@
         <v>715238.0</v>
       </c>
       <c r="B161" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="C161" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E161" s="1" t="s">
         <v>494</v>
-      </c>
-      <c r="C161" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E161" s="1" t="s">
-        <v>492</v>
       </c>
       <c r="F161" s="1">
         <v>715237.0</v>
@@ -9163,13 +9169,13 @@
         <v>26</v>
       </c>
       <c r="I161" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J161" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="K161" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="L161" s="1">
         <v>12.0</v>
@@ -9186,7 +9192,7 @@
         <v>715112.0</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C162" s="1">
         <v>10.0</v>
@@ -9207,22 +9213,22 @@
         <v>26</v>
       </c>
       <c r="I162" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J162" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="K162" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L162" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M162" s="1" t="s">
         <v>19</v>
       </c>
       <c r="N162" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="163">
@@ -9230,7 +9236,7 @@
         <v>715173.0</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C163" s="1">
         <v>10.0</v>
@@ -9251,10 +9257,10 @@
         <v>26</v>
       </c>
       <c r="I163" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J163" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="K163" s="1" t="s">
         <v>22</v>
@@ -9266,7 +9272,7 @@
         <v>19</v>
       </c>
       <c r="N163" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="164">
@@ -9274,7 +9280,7 @@
         <v>715193.0</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C164" s="1">
         <v>10.0</v>
@@ -9295,10 +9301,10 @@
         <v>26</v>
       </c>
       <c r="I164" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J164" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="K164" s="1" t="s">
         <v>22</v>
@@ -9310,7 +9316,7 @@
         <v>19</v>
       </c>
       <c r="N164" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="165">
@@ -9318,7 +9324,7 @@
         <v>715171.0</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C165" s="1">
         <v>10.0</v>
@@ -9339,10 +9345,10 @@
         <v>26</v>
       </c>
       <c r="I165" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J165" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="K165" s="1" t="s">
         <v>22</v>
@@ -9354,7 +9360,7 @@
         <v>19</v>
       </c>
       <c r="N165" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="166">
@@ -9362,7 +9368,7 @@
         <v>724441.0</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C166" s="1">
         <v>10.0</v>
@@ -9371,7 +9377,7 @@
         <v>15</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="F166" s="1">
         <v>724000.0</v>
@@ -9383,13 +9389,13 @@
         <v>19</v>
       </c>
       <c r="I166" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J166" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="K166" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="L166" s="1" t="s">
         <v>49</v>
@@ -9406,7 +9412,7 @@
         <v>724443.0</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C167" s="1">
         <v>10.0</v>
@@ -9415,7 +9421,7 @@
         <v>15</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>18</v>
@@ -9427,13 +9433,13 @@
         <v>19</v>
       </c>
       <c r="I167" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J167" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="K167" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="L167" s="1" t="s">
         <v>49</v>
@@ -9450,7 +9456,7 @@
         <v>724444.0</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C168" s="1">
         <v>10.0</v>
@@ -9459,7 +9465,7 @@
         <v>15</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>18</v>
@@ -9471,16 +9477,16 @@
         <v>19</v>
       </c>
       <c r="I168" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J168" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="K168" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="L168" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M168" s="1" t="s">
         <v>26</v>
@@ -9494,7 +9500,7 @@
         <v>724300.0</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C169" s="1">
         <v>10.0</v>
@@ -9515,13 +9521,13 @@
         <v>26</v>
       </c>
       <c r="I169" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J169" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K169" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="L169" s="1" t="s">
         <v>44</v>
@@ -9538,7 +9544,7 @@
         <v>724310.0</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C170" s="1">
         <v>10.0</v>
@@ -9547,7 +9553,7 @@
         <v>15</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="F170" s="1">
         <v>724300.0</v>
@@ -9559,13 +9565,13 @@
         <v>26</v>
       </c>
       <c r="I170" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J170" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="K170" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="L170" s="1" t="s">
         <v>44</v>
@@ -9582,7 +9588,7 @@
         <v>724311.0</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C171" s="1">
         <v>10.0</v>
@@ -9591,10 +9597,10 @@
         <v>15</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="G171" s="1" t="s">
         <v>18</v>
@@ -9603,16 +9609,16 @@
         <v>19</v>
       </c>
       <c r="I171" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J171" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="K171" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="L171" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M171" s="1" t="s">
         <v>26</v>
@@ -9626,7 +9632,7 @@
         <v>765000.0</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C172" s="1">
         <v>10.0</v>
@@ -9647,10 +9653,10 @@
         <v>26</v>
       </c>
       <c r="I172" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="J172" s="1" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="K172" s="1" t="s">
         <v>22</v>
@@ -9670,7 +9676,7 @@
         <v>765020.0</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C173" s="1">
         <v>10.0</v>
@@ -9679,7 +9685,7 @@
         <v>15</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="F173" s="1">
         <v>765000.0</v>
@@ -9691,13 +9697,13 @@
         <v>26</v>
       </c>
       <c r="I173" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="J173" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="K173" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="L173" s="1" t="s">
         <v>44</v>
@@ -9714,7 +9720,7 @@
         <v>765040.0</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C174" s="1">
         <v>10.0</v>
@@ -9723,7 +9729,7 @@
         <v>15</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="F174" s="1">
         <v>765020.0</v>
@@ -9735,10 +9741,10 @@
         <v>26</v>
       </c>
       <c r="I174" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="J174" s="1" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="K174" s="1" t="s">
         <v>22</v>
@@ -9758,7 +9764,7 @@
         <v>765060.0</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C175" s="1">
         <v>10.0</v>
@@ -9767,7 +9773,7 @@
         <v>15</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="F175" s="1">
         <v>765060.0</v>
@@ -9779,13 +9785,13 @@
         <v>19</v>
       </c>
       <c r="I175" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="J175" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="K175" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="L175" s="1" t="s">
         <v>49</v>
@@ -9802,7 +9808,7 @@
         <v>765315.0</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C176" s="1">
         <v>10.0</v>
@@ -9811,7 +9817,7 @@
         <v>15</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F176" s="1">
         <v>765310.0</v>
@@ -9823,10 +9829,10 @@
         <v>26</v>
       </c>
       <c r="I176" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="J176" s="1" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="K176" s="1" t="s">
         <v>22</v>
@@ -9846,7 +9852,7 @@
         <v>765320.0</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C177" s="1">
         <v>10.0</v>
@@ -9855,7 +9861,7 @@
         <v>15</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="F177" s="1">
         <v>765315.0</v>
@@ -9867,10 +9873,10 @@
         <v>19</v>
       </c>
       <c r="I177" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="J177" s="1" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K177" s="1" t="s">
         <v>22</v>
@@ -9890,7 +9896,7 @@
         <v>765325.0</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C178" s="1">
         <v>10.0</v>
@@ -9899,7 +9905,7 @@
         <v>15</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="F178" s="1">
         <v>765320.0</v>
@@ -9911,10 +9917,10 @@
         <v>19</v>
       </c>
       <c r="I178" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="J178" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="K178" s="1" t="s">
         <v>22</v>
@@ -9934,7 +9940,7 @@
         <v>765300.0</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C179" s="1">
         <v>10.0</v>
@@ -9955,10 +9961,10 @@
         <v>26</v>
       </c>
       <c r="I179" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="J179" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="K179" s="1" t="s">
         <v>22</v>
@@ -9978,7 +9984,7 @@
         <v>765310.0</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C180" s="1">
         <v>10.0</v>
@@ -9987,7 +9993,7 @@
         <v>15</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="F180" s="1">
         <v>765310.0</v>
@@ -9999,10 +10005,10 @@
         <v>26</v>
       </c>
       <c r="I180" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="J180" s="1" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="K180" s="1" t="s">
         <v>22</v>
@@ -10022,7 +10028,7 @@
         <v>765100.0</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C181" s="1">
         <v>10.0</v>
@@ -10031,7 +10037,7 @@
         <v>15</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>18</v>
@@ -10043,10 +10049,10 @@
         <v>26</v>
       </c>
       <c r="I181" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="J181" s="1" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="K181" s="1" t="s">
         <v>22</v>
@@ -10066,7 +10072,7 @@
         <v>765120.0</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C182" s="1">
         <v>10.0</v>
@@ -10075,7 +10081,7 @@
         <v>15</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="F182" s="1">
         <v>765120.0</v>
@@ -10087,10 +10093,10 @@
         <v>26</v>
       </c>
       <c r="I182" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="J182" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="K182" s="1" t="s">
         <v>22</v>
@@ -10110,7 +10116,7 @@
         <v>765140.0</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C183" s="1">
         <v>10.0</v>
@@ -10119,7 +10125,7 @@
         <v>15</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="F183" s="1">
         <v>765120.0</v>
@@ -10131,10 +10137,10 @@
         <v>26</v>
       </c>
       <c r="I183" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="J183" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="K183" s="1" t="s">
         <v>22</v>
@@ -10154,7 +10160,7 @@
         <v>765162.0</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C184" s="1">
         <v>10.0</v>
@@ -10163,7 +10169,7 @@
         <v>15</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="F184" s="1">
         <v>765140.0</v>
@@ -10175,10 +10181,10 @@
         <v>19</v>
       </c>
       <c r="I184" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="J184" s="1" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="K184" s="1" t="s">
         <v>22</v>
@@ -10198,7 +10204,7 @@
         <v>765191.0</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C185" s="1">
         <v>10.0</v>
@@ -10207,7 +10213,7 @@
         <v>15</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="F185" s="1">
         <v>765162.0</v>
@@ -10219,10 +10225,10 @@
         <v>19</v>
       </c>
       <c r="I185" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="J185" s="1" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="K185" s="1" t="s">
         <v>22</v>
@@ -10242,7 +10248,7 @@
         <v>765080.0</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C186" s="1">
         <v>10.0</v>
@@ -10251,7 +10257,7 @@
         <v>15</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="F186" s="1">
         <v>765060.0</v>
@@ -10263,16 +10269,16 @@
         <v>19</v>
       </c>
       <c r="I186" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="J186" s="1" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="K186" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L186" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M186" s="1" t="s">
         <v>26</v>
@@ -10286,7 +10292,7 @@
         <v>765400.0</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C187" s="1">
         <v>10.0</v>
@@ -10307,10 +10313,10 @@
         <v>26</v>
       </c>
       <c r="I187" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="J187" s="1" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="K187" s="1" t="s">
         <v>22</v>
@@ -10330,7 +10336,7 @@
         <v>765401.0</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C188" s="1">
         <v>10.0</v>
@@ -10339,7 +10345,7 @@
         <v>15</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="F188" s="1">
         <v>765400.0</v>
@@ -10351,10 +10357,10 @@
         <v>26</v>
       </c>
       <c r="I188" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="J188" s="1" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="K188" s="1" t="s">
         <v>22</v>
@@ -10374,7 +10380,7 @@
         <v>765402.0</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C189" s="1">
         <v>10.0</v>
@@ -10383,7 +10389,7 @@
         <v>15</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="F189" s="1">
         <v>765401.0</v>
@@ -10395,10 +10401,10 @@
         <v>26</v>
       </c>
       <c r="I189" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="J189" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="K189" s="1" t="s">
         <v>22</v>
@@ -10418,7 +10424,7 @@
         <v>714824.0</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C190" s="1">
         <v>10.0</v>
@@ -10439,13 +10445,13 @@
         <v>19</v>
       </c>
       <c r="I190" s="1" t="s">
-        <v>413</v>
+        <v>138</v>
       </c>
       <c r="J190" s="1" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="K190" s="1" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="L190" s="1">
         <v>12.0</v>
@@ -10462,7 +10468,7 @@
         <v>797253.0</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C191" s="1">
         <v>10.0</v>
@@ -10471,10 +10477,10 @@
         <v>15</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G191" s="1" t="s">
         <v>18</v>
@@ -10483,16 +10489,16 @@
         <v>26</v>
       </c>
       <c r="I191" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J191" s="1" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="K191" s="1" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="L191" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M191" s="1" t="s">
         <v>26</v>
@@ -10506,7 +10512,7 @@
         <v>797256.0</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C192" s="1">
         <v>10.0</v>
@@ -10515,10 +10521,10 @@
         <v>15</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="G192" s="1" t="s">
         <v>18</v>
@@ -10527,16 +10533,16 @@
         <v>26</v>
       </c>
       <c r="I192" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J192" s="1" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="K192" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="L192" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M192" s="1" t="s">
         <v>26</v>
@@ -10550,7 +10556,7 @@
         <v>710418.0</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C193" s="1">
         <v>10.0</v>
@@ -10571,13 +10577,13 @@
         <v>26</v>
       </c>
       <c r="I193" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J193" s="1" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="K193" s="1" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="L193" s="1" t="s">
         <v>44</v>
@@ -10594,7 +10600,7 @@
         <v>711267.0</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C194" s="1">
         <v>10.0</v>
@@ -10603,10 +10609,10 @@
         <v>15</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="G194" s="1" t="s">
         <v>18</v>
@@ -10615,13 +10621,13 @@
         <v>26</v>
       </c>
       <c r="I194" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J194" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K194" s="1" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="L194" s="1" t="s">
         <v>49</v>
@@ -10638,7 +10644,7 @@
         <v>711291.0</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C195" s="1">
         <v>10.0</v>
@@ -10647,7 +10653,7 @@
         <v>15</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="F195" s="1">
         <v>711225.0</v>
@@ -10659,10 +10665,10 @@
         <v>26</v>
       </c>
       <c r="I195" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J195" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="K195" s="1" t="s">
         <v>18</v>
@@ -10682,7 +10688,7 @@
         <v>711227.0</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C196" s="1">
         <v>10.0</v>
@@ -10691,7 +10697,7 @@
         <v>15</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="F196" s="1">
         <v>711225.0</v>
@@ -10703,10 +10709,10 @@
         <v>26</v>
       </c>
       <c r="I196" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J196" s="1" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="K196" s="1" t="s">
         <v>18</v>
@@ -10726,7 +10732,7 @@
         <v>715102.0</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C197" s="1">
         <v>10.0</v>
@@ -10735,7 +10741,7 @@
         <v>15</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="F197" s="1">
         <v>715101.0</v>
@@ -10747,16 +10753,16 @@
         <v>26</v>
       </c>
       <c r="I197" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J197" s="1" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="K197" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L197" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M197" s="1" t="s">
         <v>19</v>
@@ -10767,10 +10773,10 @@
     </row>
     <row r="198">
       <c r="A198" s="2" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C198" s="1">
         <v>10.0</v>
@@ -10779,7 +10785,7 @@
         <v>15</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>18</v>
@@ -10791,13 +10797,13 @@
         <v>26</v>
       </c>
       <c r="I198" s="1" t="s">
-        <v>413</v>
+        <v>127</v>
       </c>
       <c r="J198" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="K198" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L198" s="1" t="s">
         <v>44</v>

--- a/ehs_courses_matched.xlsx
+++ b/ehs_courses_matched.xlsx
@@ -244,7 +244,7 @@
     <t>Students engage in an extensive survey of the American literary movements: Puritans, Rationalists, Romantics, Realists, and Modernists. Some of the texts include The Great Gatsby and excerpts from the Holt Literature and Language Arts textbook. Students learn analytical and creative thinking skills to look at the world more critically. This class is designed to stimulate and improve students’ critical thinking, reading, writing, vocabulary, language usage, and communication skills in order to help students be college and career ready. Students also prepare to take the state SBAC (Smarter Balanced Assessment Consortium) exam in May. Homework in this course serves multiple purposes and follows district policy regarding homework and grading. Students complete homework to finish work started in class and engage further in material covered in class. Assignments include reading novels, analyzing texts, practicing reading comprehension skills and writing, and preparing for projects, seminars, and other class activities.</t>
   </si>
   <si>
-    <t>AP English Language and Composition</t>
+    <t>AP English Language and Composition (AP Lang)</t>
   </si>
   <si>
     <t>This college level course is designed for students motivated to challenge themselves through extensive reading and writing. The curriculum follows American Literature selections, and highlights classic and contemporary non-fiction. Students read independently, keep notes, write essays, analyze the use of rhetorical devices, and engage in frequent Socratic seminars. Homework will primarily focus on intensive reading of college-level texts and on writing assignments designed to develop sophisticated analysis and argument skills. Each spring, students have the option to take the Advanced Placement exam in English Language and Composition. If students pass, they earn college credit.</t>
@@ -334,7 +334,7 @@
     <t>Podcasting and Storytelling is a semester course that will explore the medium of podcasting, specifically in the context of narrative storytelling.  The foundation of the course is an exploration into the elements of storytelling, focusing on the rhetorical choices that a writer/ producer must consider (structure, diction, evidence, audience, voice and tone).  Students will begin the semester with a teacher-selected core reading list that allows them to explore and build awareness of the art of storytelling.  As the semester progresses, students will work in collaborative groups with the instructor to create their own reading lists, which will be inquiry-based and will inform them more about the subject that they choose for their own podcast.  The capstone project for this class is the creation of an original podcast that incorporates student research, interviews, and original writing, and that will be produced and published for our school audience.</t>
   </si>
   <si>
-    <t>AP English Literature and Composition</t>
+    <t>AP English Literature and Composition (AP Lit)</t>
   </si>
   <si>
     <t>This intensive college-level course is designed for the student who has demonstrated exceptional interest and ability in English. Students are challenged to read independently from a variety of genres, analyze the works, keep notes, write in-class essays and longer papers, and engage in small and large group discussions. Summer reading is assigned and students may earn college credit when they take the required Advanced Placement exam in English Literature.</t>
@@ -424,7 +424,7 @@
     <t>Students build an understanding of the economic, political, and social changes that have occurred in United States history.  This course encourages students to weigh evidence and interpret problems presented by historians.Through assessment and critical analysis of historical documents and interpretations of them, students learn to analyze data, form conclusions, and present well-reasoned, persuasive arguments in written form.  Homework for this course is an invaluable tool used to introduce, reinforce, and help with comprehension with respect to course material.</t>
   </si>
   <si>
-    <t>AP United States Government and Politics</t>
+    <t>AP United States Government and Politics (AP Gov)</t>
   </si>
   <si>
     <t>Civics/Economics</t>
@@ -514,7 +514,7 @@
     <t>Understanding and applying geometry theorems and definitions is expected.  All California Standards for Geometry are included in the curriculum.  Students will learn the basics of geometry and its language, reasoning skills and methods of proof, shapes of two and three dimensions and their properties and size measurements, similarity, geometric probability and transformations.</t>
   </si>
   <si>
-    <t>AP Human Geography</t>
+    <t>AP Human Geography (HUG)</t>
   </si>
   <si>
     <t>AP Human Geography introduces high school students to college-level introductory human geography or cultural geography. The content is presented thematically rather than regionally and is organized around the discipline’s main subfields: economic geography, cultural geography, political geography, and urban geography. The approach is spatial and problem oriented. Case studies are drawn from all world regions, with an emphasis on understanding the world in which we live today. Historical information serves to enrich analysis of the impacts of phenomena such as globalization, colonialism, and human–environment relationships on places, regions, cultural landscapes, and patterns of interaction. The goal for the course is for students to become more geoliterate, more engaged in contemporary global issues, and more informed about multicultural viewpoints. They will develop skills in approaching problems geographically, using maps and geospatial technologies, thinking critically about texts and graphic images, interpreting cultural landscapes, and applying geographic concepts such as scale, region, diffusion, interdependence, and spatial interaction, among others. Students will see geography as a discipline relevant to the world in which they live; as a source of ideas for identifying, clarifying, and solving problems at various scales; and as a key component of building global citizenship and environmental stewardship.</t>
@@ -832,7 +832,7 @@
     <t>Show Choir is an open course offered to students who qualify for show choir music, theatre and dance instruction through audition. Students must show proficiency in reading music, playing an instrument and/or singing with proper choral tone. Students must demonstrate the ability to move/dance. This course is designed to increase the vocal skills and performance levels of each student by presenting a rigorous repertoire from various historical periods and cultures. Students will sing a wide range of literature such as Musical Theatre, Pop, Jazz, and Folk. From the study of these various styles, students will attain enhanced awareness of the history and events surrounding the development of choral literature. Correct stylistic performance and interpretation of the different repertoires will be emphasized. Students are required to participate in performances outside the regular school day throughout the academic year.</t>
   </si>
   <si>
-    <t>Freshman P.E.</t>
+    <t>Freshman PE</t>
   </si>
   <si>
     <t>PE is required in Grade 9.  Components of Nutrition, Fitness and Safety from the California Physical Health Standards are included in the curriculum.  All freshmen will take the California Physical Performance and Health Related Test during the third quarter.  Also covered are: team sports, individual sports, aquatics, body development and the introduction to weight-lifting. This is a required course for graduation, as students must pass the FitnessGram.</t>
@@ -955,7 +955,7 @@
     <t>5-8 hours a week, preview and practice to support conceptual knowledge, critical thinking, and communicating scientific topics in writing. “Extension” assignments may be required to analyze and communicate laboratory exercises, and to review problems to strengthen biology topics covered in previous courses.</t>
   </si>
   <si>
-    <t>AP Environmental Science</t>
+    <t>AP Environmental Science (APES)</t>
   </si>
   <si>
     <t>Concurrent enrollment in or successful completion of Algebra II, plus successful completion of at least one other Laboratory science course.</t>
@@ -1033,7 +1033,7 @@
     <t>60 minutes a day, often more (intense, college-level problem-solving)</t>
   </si>
   <si>
-    <t>Principles of Biomedical Science (PLTW)</t>
+    <t>Principles of Biomedical Science (PLTW) (PBS)</t>
   </si>
   <si>
     <t>Concurrent enrollment or completion of Biology and Biomedical Pathway application completed</t>
@@ -1126,7 +1126,7 @@
     <t>Specialized Academic Instruction provides students with specially designed instruction and support necessary for success in high school and to address Individualized Education Program goals. Students receive instruction that parallels the second semester of the standard Algebra curriculum. This is the second year of a two-year algebra course taught for students with an IEP. The course includes opportunities in computation, math facts, and numbers sense and integrates Algebra, Geometry, coordinate geometry, patterns, and functions. Students work on problem-solving techniques and real-life modeling.</t>
   </si>
   <si>
-    <t>Human Body Systems (PLTW)</t>
+    <t>Human Body Systems (PLTW) (HBS)</t>
   </si>
   <si>
     <t>Successful completion of Biology and Biomedical Pathway application completed</t>
@@ -1138,7 +1138,7 @@
     <t>1-2 hours a week; review and extension, especially Internet research and analysis of concepts learned. A detailed lab notebook will be kept.</t>
   </si>
   <si>
-    <t>Honors Biomedical Innovation (HP)  (PLTW)</t>
+    <t>Honors Biomedical Innovation (HP) (PLTW) (HBI)</t>
   </si>
   <si>
     <t>Successful completion of Biology and Chemistry (successful completion of an Honors or AP level science class recommended)</t>
@@ -1150,7 +1150,7 @@
     <t>Biomedical Innovation (PLTW) is a UC “G” elective Honors course. Senior students apply their knowledge and skills to answer questions and solve problems related to biomedical sciences. Problems include: designing an effective emergency room, exploring human physiology through direct testing, designing a medical innovation, investigating environmental health, combating a public health issue and an independent project of their choice. Much of this work requires a strong background in Biology, Chemistry and Medicine. Students must have a good work ethic and be able to work independently to meet deadlines and prepare presentations. There is a cumulative final exam at the end of the second semester that tests knowledge from both semesters.</t>
   </si>
   <si>
-    <t>Honors Medical Interventions (HP) (PLTW)</t>
+    <t>Honors Medical Interventions (HP) (PLTW) (HMI)</t>
   </si>
   <si>
     <t>Successful completion of an Honors or AP level science course, participation in PLTW Biomedical Pathway</t>
@@ -10084,7 +10084,7 @@
         <v>556</v>
       </c>
       <c r="F182" s="1">
-        <v>765120.0</v>
+        <v>765100.0</v>
       </c>
       <c r="G182" s="1" t="s">
         <v>18</v>

--- a/ehs_courses_matched.xlsx
+++ b/ehs_courses_matched.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2274" uniqueCount="604">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2301" uniqueCount="614">
   <si>
     <t>Course Number</t>
   </si>
@@ -127,7 +127,10 @@
     <t>PLTW Honors Digital Electronics (DE)</t>
   </si>
   <si>
-    <t>Successful completion of POE or Engineering Teacher Recommendation</t>
+    <t>Successful completion of POE, CSA, or Engineering Teacher Recommendation</t>
+  </si>
+  <si>
+    <t>(717010, 717018)</t>
   </si>
   <si>
     <t>Digital electronics is the foundation of all modern electronic devices such as mobile phones, MP3 players, laptop computers, digital cameras and high-definition televisions. Students are introduced to the process of combinational and sequential logic design, while designing their own electronic circuits for design implementation. Students also continue to refine their communication skills through engineering standards and technical documentation.This course is a specialization-level course designed to follow the Project Lead the Way Engineering foundational courses.</t>
@@ -493,7 +496,7 @@
     <t>Algebra I</t>
   </si>
   <si>
-    <t>Mathematics</t>
+    <t>Math</t>
   </si>
   <si>
     <t>This course is a State of California graduation requirement.  Topics covered include graphing and writing linear equations and inequalities, systems of equations and inequalities, exponential expressions, operations with polynomials and radicals, quadratic equations, graphing functions including exponential, cubic, and absolute value functions. Students must pass both semesters of this course to meet the state high school graduation requirements and move on to Geometry.</t>
@@ -694,7 +697,7 @@
     <t>60 minutes a day, plus additional time for larger projects.</t>
   </si>
   <si>
-    <t>Student Assistant (Semester)</t>
+    <t>Student Assistant (Semester) (TA)</t>
   </si>
   <si>
     <t>Teacher recommendation, minimum 2.5 GPA prior semester, excellent attendance and behavior</t>
@@ -703,7 +706,7 @@
     <t>Limited to one Student Assistant class per semester. Students who have special skills in typing, filing, tutoring, or specific subjects may apply for positions with teachers, secretaries and other school personnel provided they first have their counselor’s approval. All Student Assistant positions must be confirmed in writing on a specific form secured from the counselor.</t>
   </si>
   <si>
-    <t>Student Assistant (Year)</t>
+    <t>Student Assistant (Year) (TA)</t>
   </si>
   <si>
     <t>Student Leadership</t>
@@ -1823,6 +1826,33 @@
   </si>
   <si>
     <t xml:space="preserve">Students receive instruction that parallels the standard World History programs.  Accommodated presentations include information on the geography, history, cultures, economics, and politics of the major world regions. </t>
+  </si>
+  <si>
+    <t>SEMESTER_PE</t>
+  </si>
+  <si>
+    <t>Summer PE (Semester - 3 weeks)</t>
+  </si>
+  <si>
+    <t>3 weeks</t>
+  </si>
+  <si>
+    <t>Students take PE over the summer from an institution to fulfill PE credits. 1 semester summer course is 3 weeks.</t>
+  </si>
+  <si>
+    <t>Summer</t>
+  </si>
+  <si>
+    <t>YEAR_PE</t>
+  </si>
+  <si>
+    <t>Summer PE (Year - 6 weeks)</t>
+  </si>
+  <si>
+    <t>6 weeks</t>
+  </si>
+  <si>
+    <t>Students take PE over the summer from an institution to fulfill PE credits. 1 year summer course is 6 weeks.</t>
   </si>
 </sst>
 </file>
@@ -2295,8 +2325,8 @@
       <c r="E5" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F5" s="1">
-        <v>717010.0</v>
+      <c r="F5" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>18</v>
@@ -2308,10 +2338,10 @@
         <v>20</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L5" s="1">
         <v>12.0</v>
@@ -2328,7 +2358,7 @@
         <v>717017.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C6" s="1">
         <v>10.0</v>
@@ -2352,13 +2382,13 @@
         <v>27</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>26</v>
@@ -2372,7 +2402,7 @@
         <v>717016.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C7" s="1">
         <v>10.0</v>
@@ -2381,7 +2411,7 @@
         <v>15</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F7" s="1">
         <v>717017.0</v>
@@ -2396,13 +2426,13 @@
         <v>20</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>26</v>
@@ -2416,7 +2446,7 @@
         <v>717018.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C8" s="1">
         <v>10.0</v>
@@ -2425,7 +2455,7 @@
         <v>15</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F8" s="1">
         <v>717016.0</v>
@@ -2440,10 +2470,10 @@
         <v>20</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>30</v>
@@ -2460,7 +2490,7 @@
         <v>753661.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C9" s="1">
         <v>10.0</v>
@@ -2469,7 +2499,7 @@
         <v>15</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>18</v>
@@ -2481,10 +2511,10 @@
         <v>26</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>22</v>
@@ -2504,7 +2534,7 @@
         <v>753662.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C10" s="1">
         <v>10.0</v>
@@ -2525,10 +2555,10 @@
         <v>26</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>22</v>
@@ -2548,7 +2578,7 @@
         <v>753555.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C11" s="1">
         <v>10.0</v>
@@ -2569,10 +2599,10 @@
         <v>26</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>22</v>
@@ -2592,7 +2622,7 @@
         <v>753560.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C12" s="1">
         <v>10.0</v>
@@ -2613,10 +2643,10 @@
         <v>26</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>18</v>
@@ -2636,7 +2666,7 @@
         <v>717015.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C13" s="1">
         <v>10.0</v>
@@ -2660,13 +2690,13 @@
         <v>20</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>29</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>26</v>
@@ -2680,7 +2710,7 @@
         <v>717010.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C14" s="1">
         <v>10.0</v>
@@ -2689,10 +2719,10 @@
         <v>15</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>18</v>
@@ -2704,13 +2734,13 @@
         <v>20</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>26</v>
@@ -2724,7 +2754,7 @@
         <v>715242.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C15" s="1">
         <v>10.0</v>
@@ -2733,7 +2763,7 @@
         <v>15</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F15" s="1">
         <v>717010.0</v>
@@ -2748,7 +2778,7 @@
         <v>20</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>29</v>
@@ -2760,7 +2790,7 @@
         <v>19</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16">
@@ -2768,7 +2798,7 @@
         <v>753681.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C16" s="1">
         <v>10.0</v>
@@ -2777,7 +2807,7 @@
         <v>15</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>18</v>
@@ -2789,10 +2819,10 @@
         <v>26</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K16" s="1" t="s">
         <v>22</v>
@@ -2812,7 +2842,7 @@
         <v>753713.0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C17" s="1">
         <v>10.0</v>
@@ -2833,13 +2863,13 @@
         <v>19</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L17" s="1">
         <v>11.0</v>
@@ -2856,16 +2886,16 @@
         <v>753386.0</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C18" s="1">
         <v>5.0</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>18</v>
@@ -2877,10 +2907,10 @@
         <v>26</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K18" s="1" t="s">
         <v>22</v>
@@ -2900,7 +2930,7 @@
         <v>754001.0</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C19" s="1">
         <v>10.0</v>
@@ -2909,7 +2939,7 @@
         <v>15</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>18</v>
@@ -2924,13 +2954,13 @@
         <v>20</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>26</v>
@@ -2944,7 +2974,7 @@
         <v>754003.0</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C20" s="1">
         <v>10.0</v>
@@ -2953,7 +2983,7 @@
         <v>15</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>18</v>
@@ -2965,16 +2995,16 @@
         <v>26</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>26</v>
@@ -2988,7 +3018,7 @@
         <v>754005.0</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C21" s="1">
         <v>10.0</v>
@@ -2997,7 +3027,7 @@
         <v>15</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>18</v>
@@ -3009,10 +3039,10 @@
         <v>26</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>22</v>
@@ -3032,7 +3062,7 @@
         <v>776328.0</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C22" s="1">
         <v>10.0</v>
@@ -3053,13 +3083,13 @@
         <v>26</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L22" s="1">
         <v>9.0</v>
@@ -3076,16 +3106,16 @@
         <v>753353.0</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C23" s="1">
         <v>5.0</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F23" s="1">
         <v>753681.0</v>
@@ -3097,10 +3127,10 @@
         <v>26</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K23" s="1" t="s">
         <v>22</v>
@@ -3120,16 +3150,16 @@
         <v>753361.0</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C24" s="1">
         <v>5.0</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F24" s="1">
         <v>753681.0</v>
@@ -3141,10 +3171,10 @@
         <v>26</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K24" s="1" t="s">
         <v>22</v>
@@ -3164,16 +3194,16 @@
         <v>753387.0</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C25" s="1">
         <v>5.0</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F25" s="1">
         <v>753681.0</v>
@@ -3185,10 +3215,10 @@
         <v>26</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K25" s="1" t="s">
         <v>22</v>
@@ -3208,16 +3238,16 @@
         <v>753390.0</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C26" s="1">
         <v>5.0</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F26" s="1">
         <v>753681.0</v>
@@ -3229,10 +3259,10 @@
         <v>26</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K26" s="1" t="s">
         <v>22</v>
@@ -3252,16 +3282,16 @@
         <v>753332.0</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C27" s="1">
         <v>5.0</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F27" s="1">
         <v>753681.0</v>
@@ -3273,10 +3303,10 @@
         <v>26</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K27" s="1" t="s">
         <v>22</v>
@@ -3296,7 +3326,7 @@
         <v>753710.0</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C28" s="1">
         <v>10.0</v>
@@ -3317,13 +3347,13 @@
         <v>19</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L28" s="1">
         <v>12.0</v>
@@ -3340,7 +3370,7 @@
         <v>754000.0</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C29" s="1">
         <v>10.0</v>
@@ -3349,7 +3379,7 @@
         <v>15</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>18</v>
@@ -3361,16 +3391,16 @@
         <v>26</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K29" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>26</v>
@@ -3384,7 +3414,7 @@
         <v>753391.0</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C30" s="1">
         <v>10.0</v>
@@ -3393,7 +3423,7 @@
         <v>15</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F30" s="1">
         <v>753681.0</v>
@@ -3405,10 +3435,10 @@
         <v>26</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>22</v>
@@ -3428,16 +3458,16 @@
         <v>753351.0</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C31" s="1">
         <v>5.0</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F31" s="1">
         <v>753681.0</v>
@@ -3449,10 +3479,10 @@
         <v>26</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K31" s="1" t="s">
         <v>22</v>
@@ -3472,7 +3502,7 @@
         <v>753715.0</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C32" s="1">
         <v>10.0</v>
@@ -3481,7 +3511,7 @@
         <v>15</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F32" s="1">
         <v>753681.0</v>
@@ -3493,10 +3523,10 @@
         <v>26</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K32" s="1" t="s">
         <v>22</v>
@@ -3516,16 +3546,16 @@
         <v>753389.0</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C33" s="1">
         <v>5.0</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F33" s="1">
         <v>753681.0</v>
@@ -3537,10 +3567,10 @@
         <v>26</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K33" s="1" t="s">
         <v>22</v>
@@ -3560,7 +3590,7 @@
         <v>776004.0</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C34" s="1">
         <v>10.0</v>
@@ -3581,16 +3611,16 @@
         <v>26</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M34" s="1" t="s">
         <v>26</v>
@@ -3604,13 +3634,13 @@
         <v>714802.0</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C35" s="1">
         <v>5.0</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>18</v>
@@ -3625,16 +3655,16 @@
         <v>26</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M35" s="1" t="s">
         <v>26</v>
@@ -3648,34 +3678,34 @@
         <v>714838.0</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C36" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="K36" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="C36" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="K36" s="1" t="s">
-        <v>126</v>
       </c>
       <c r="L36" s="1">
         <v>10.0</v>
@@ -3692,7 +3722,7 @@
         <v>714847.0</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C37" s="1">
         <v>10.0</v>
@@ -3713,13 +3743,13 @@
         <v>19</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L37" s="1">
         <v>10.0</v>
@@ -3736,7 +3766,7 @@
         <v>714818.0</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C38" s="1">
         <v>10.0</v>
@@ -3757,13 +3787,13 @@
         <v>26</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L38" s="1">
         <v>11.0</v>
@@ -3780,7 +3810,7 @@
         <v>714822.0</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C39" s="1">
         <v>10.0</v>
@@ -3801,10 +3831,10 @@
         <v>19</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K39" s="1" t="s">
         <v>18</v>
@@ -3824,13 +3854,13 @@
         <v>714828.0</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C40" s="1">
         <v>5.0</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>18</v>
@@ -3845,13 +3875,13 @@
         <v>19</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L40" s="1">
         <v>12.0</v>
@@ -3868,7 +3898,7 @@
         <v>717240.0</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C41" s="1">
         <v>10.0</v>
@@ -3892,13 +3922,13 @@
         <v>20</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K41" s="1" t="s">
         <v>18</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M41" s="1" t="s">
         <v>26</v>
@@ -3912,13 +3942,13 @@
         <v>714823.0</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C42" s="1">
         <v>5.0</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>18</v>
@@ -3933,13 +3963,13 @@
         <v>26</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L42" s="1">
         <v>12.0</v>
@@ -3956,13 +3986,13 @@
         <v>714827.0</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C43" s="1">
         <v>5.0</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>18</v>
@@ -3977,13 +4007,13 @@
         <v>19</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L43" s="1">
         <v>12.0</v>
@@ -4000,13 +4030,13 @@
         <v>714829.0</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C44" s="1">
         <v>5.0</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>18</v>
@@ -4021,13 +4051,13 @@
         <v>19</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L44" s="1">
         <v>12.0</v>
@@ -4044,13 +4074,13 @@
         <v>714826.0</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C45" s="1">
         <v>5.0</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>18</v>
@@ -4065,13 +4095,13 @@
         <v>26</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L45" s="1">
         <v>12.0</v>
@@ -4088,13 +4118,13 @@
         <v>714805.0</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C46" s="1">
         <v>5.0</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>18</v>
@@ -4112,13 +4142,13 @@
         <v>20</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M46" s="1" t="s">
         <v>26</v>
@@ -4132,13 +4162,13 @@
         <v>717242.0</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C47" s="1">
         <v>5.0</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>18</v>
@@ -4156,13 +4186,13 @@
         <v>20</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M47" s="1" t="s">
         <v>26</v>
@@ -4176,16 +4206,16 @@
         <v>717241.0</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C48" s="1">
         <v>5.0</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F48" s="1">
         <v>797060.0</v>
@@ -4200,13 +4230,13 @@
         <v>20</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M48" s="1" t="s">
         <v>26</v>
@@ -4220,7 +4250,7 @@
         <v>797060.0</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C49" s="1">
         <v>10.0</v>
@@ -4241,16 +4271,16 @@
         <v>26</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M49" s="1" t="s">
         <v>26</v>
@@ -4264,7 +4294,7 @@
         <v>797100.0</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C50" s="1">
         <v>10.0</v>
@@ -4273,7 +4303,7 @@
         <v>15</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F50" s="1">
         <v>797060.0</v>
@@ -4285,16 +4315,16 @@
         <v>26</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K50" s="1" t="s">
         <v>18</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M50" s="1" t="s">
         <v>26</v>
@@ -4308,7 +4338,7 @@
         <v>714800.0</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C51" s="1">
         <v>10.0</v>
@@ -4332,13 +4362,13 @@
         <v>20</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M51" s="1" t="s">
         <v>26</v>
@@ -4352,7 +4382,7 @@
         <v>714832.0</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C52" s="1">
         <v>10.0</v>
@@ -4376,10 +4406,10 @@
         <v>20</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L52" s="1" t="s">
         <v>30</v>
@@ -4396,7 +4426,7 @@
         <v>797251.0</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C53" s="1">
         <v>10.0</v>
@@ -4405,10 +4435,10 @@
         <v>15</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>18</v>
@@ -4417,16 +4447,16 @@
         <v>19</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M53" s="1" t="s">
         <v>26</v>
@@ -4440,7 +4470,7 @@
         <v>797252.0</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C54" s="1">
         <v>10.0</v>
@@ -4449,7 +4479,7 @@
         <v>15</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F54" s="1">
         <v>797251.0</v>
@@ -4461,13 +4491,13 @@
         <v>19</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L54" s="1" t="s">
         <v>30</v>
@@ -4484,7 +4514,7 @@
         <v>797255.0</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C55" s="1">
         <v>10.0</v>
@@ -4493,10 +4523,10 @@
         <v>15</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>18</v>
@@ -4505,16 +4535,16 @@
         <v>19</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M55" s="1" t="s">
         <v>26</v>
@@ -4528,7 +4558,7 @@
         <v>720000.0</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C56" s="1">
         <v>10.0</v>
@@ -4537,7 +4567,7 @@
         <v>15</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>18</v>
@@ -4552,10 +4582,10 @@
         <v>20</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L56" s="1">
         <v>9.0</v>
@@ -4572,7 +4602,7 @@
         <v>720010.0</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C57" s="1">
         <v>10.0</v>
@@ -4581,7 +4611,7 @@
         <v>15</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F57" s="1">
         <v>720000.0</v>
@@ -4596,10 +4626,10 @@
         <v>20</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L57" s="1">
         <v>10.0</v>
@@ -4616,7 +4646,7 @@
         <v>797081.0</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C58" s="1">
         <v>10.0</v>
@@ -4625,10 +4655,10 @@
         <v>15</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>18</v>
@@ -4637,16 +4667,16 @@
         <v>26</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M58" s="1" t="s">
         <v>26</v>
@@ -4660,7 +4690,7 @@
         <v>797086.0</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C59" s="1">
         <v>10.0</v>
@@ -4669,10 +4699,10 @@
         <v>15</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>18</v>
@@ -4681,16 +4711,16 @@
         <v>26</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M59" s="1" t="s">
         <v>26</v>
@@ -4704,7 +4734,7 @@
         <v>797175.0</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C60" s="1">
         <v>10.0</v>
@@ -4713,10 +4743,10 @@
         <v>15</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>18</v>
@@ -4725,16 +4755,16 @@
         <v>26</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M60" s="1" t="s">
         <v>26</v>
@@ -4748,7 +4778,7 @@
         <v>797174.0</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C61" s="1">
         <v>10.0</v>
@@ -4757,10 +4787,10 @@
         <v>15</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>18</v>
@@ -4769,16 +4799,16 @@
         <v>19</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M61" s="1" t="s">
         <v>26</v>
@@ -4792,7 +4822,7 @@
         <v>720020.0</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C62" s="1">
         <v>10.0</v>
@@ -4801,7 +4831,7 @@
         <v>15</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F62" s="1">
         <v>720010.0</v>
@@ -4816,10 +4846,10 @@
         <v>20</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L62" s="1">
         <v>11.0</v>
@@ -4836,7 +4866,7 @@
         <v>720030.0</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C63" s="1">
         <v>10.0</v>
@@ -4845,7 +4875,7 @@
         <v>15</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F63" s="1">
         <v>720020.0</v>
@@ -4860,10 +4890,10 @@
         <v>20</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L63" s="1">
         <v>12.0</v>
@@ -4880,7 +4910,7 @@
         <v>717250.0</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C64" s="1">
         <v>10.0</v>
@@ -4904,13 +4934,13 @@
         <v>20</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K64" s="1" t="s">
         <v>18</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M64" s="1" t="s">
         <v>26</v>
@@ -4924,7 +4954,7 @@
         <v>710414.0</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C65" s="1">
         <v>10.0</v>
@@ -4945,16 +4975,16 @@
         <v>26</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M65" s="1" t="s">
         <v>26</v>
@@ -4968,7 +4998,7 @@
         <v>710417.0</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C66" s="1">
         <v>10.0</v>
@@ -4977,7 +5007,7 @@
         <v>15</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F66" s="1">
         <v>710414.0</v>
@@ -4989,16 +5019,16 @@
         <v>26</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M66" s="1" t="s">
         <v>26</v>
@@ -5012,7 +5042,7 @@
         <v>717251.0</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C67" s="1">
         <v>10.0</v>
@@ -5021,7 +5051,7 @@
         <v>15</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F67" s="1">
         <v>717250.0</v>
@@ -5036,10 +5066,10 @@
         <v>20</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L67" s="1" t="s">
         <v>30</v>
@@ -5056,16 +5086,16 @@
         <v>717101.0</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C68" s="1">
         <v>5.0</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>18</v>
@@ -5080,7 +5110,7 @@
         <v>20</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K68" s="1" t="s">
         <v>18</v>
@@ -5100,7 +5130,7 @@
         <v>717100.0</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C69" s="1">
         <v>10.0</v>
@@ -5109,7 +5139,7 @@
         <v>15</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>18</v>
@@ -5124,7 +5154,7 @@
         <v>20</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K69" s="1" t="s">
         <v>18</v>
@@ -5144,7 +5174,7 @@
         <v>717140.0</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C70" s="1">
         <v>10.0</v>
@@ -5153,7 +5183,7 @@
         <v>15</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>18</v>
@@ -5168,13 +5198,13 @@
         <v>20</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K70" s="1" t="s">
         <v>18</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M70" s="1" t="s">
         <v>26</v>
@@ -5188,7 +5218,7 @@
         <v>710493.0</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C71" s="1">
         <v>10.0</v>
@@ -5209,16 +5239,16 @@
         <v>26</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M71" s="1" t="s">
         <v>26</v>
@@ -5232,7 +5262,7 @@
         <v>710200.0</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C72" s="1">
         <v>10.0</v>
@@ -5241,7 +5271,7 @@
         <v>15</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F72" s="1">
         <v>710493.0</v>
@@ -5253,16 +5283,16 @@
         <v>26</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M72" s="1" t="s">
         <v>26</v>
@@ -5276,7 +5306,7 @@
         <v>710600.0</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C73" s="1">
         <v>10.0</v>
@@ -5297,16 +5327,16 @@
         <v>26</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M73" s="1" t="s">
         <v>26</v>
@@ -5320,7 +5350,7 @@
         <v>710770.0</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C74" s="1">
         <v>10.0</v>
@@ -5329,7 +5359,7 @@
         <v>15</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>18</v>
@@ -5341,16 +5371,16 @@
         <v>26</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M74" s="1" t="s">
         <v>26</v>
@@ -5364,7 +5394,7 @@
         <v>710479.0</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C75" s="1">
         <v>10.0</v>
@@ -5385,16 +5415,16 @@
         <v>26</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M75" s="1" t="s">
         <v>26</v>
@@ -5408,37 +5438,37 @@
         <v>710480.0</v>
       </c>
       <c r="B76" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C76" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="K76" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="C76" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G76" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H76" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I76" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="J76" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="K76" s="1" t="s">
-        <v>249</v>
-      </c>
       <c r="L76" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M76" s="1" t="s">
         <v>26</v>
@@ -5452,7 +5482,7 @@
         <v>710481.0</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C77" s="1">
         <v>10.0</v>
@@ -5461,7 +5491,7 @@
         <v>15</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>18</v>
@@ -5473,16 +5503,16 @@
         <v>19</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M77" s="1" t="s">
         <v>26</v>
@@ -5496,7 +5526,7 @@
         <v>711280.0</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C78" s="1">
         <v>10.0</v>
@@ -5505,7 +5535,7 @@
         <v>15</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F78" s="1">
         <v>711225.0</v>
@@ -5517,16 +5547,16 @@
         <v>26</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K78" s="1" t="s">
         <v>18</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M78" s="1" t="s">
         <v>26</v>
@@ -5540,7 +5570,7 @@
         <v>710472.0</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C79" s="1">
         <v>10.0</v>
@@ -5549,7 +5579,7 @@
         <v>15</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>18</v>
@@ -5561,16 +5591,16 @@
         <v>19</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M79" s="1" t="s">
         <v>26</v>
@@ -5584,7 +5614,7 @@
         <v>710773.0</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C80" s="1">
         <v>10.0</v>
@@ -5593,7 +5623,7 @@
         <v>15</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>18</v>
@@ -5605,16 +5635,16 @@
         <v>19</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M80" s="1" t="s">
         <v>26</v>
@@ -5628,7 +5658,7 @@
         <v>710450.0</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C81" s="1">
         <v>10.0</v>
@@ -5649,16 +5679,16 @@
         <v>26</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M81" s="1" t="s">
         <v>26</v>
@@ -5672,7 +5702,7 @@
         <v>710451.0</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C82" s="1">
         <v>10.0</v>
@@ -5693,16 +5723,16 @@
         <v>26</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M82" s="1" t="s">
         <v>26</v>
@@ -5716,7 +5746,7 @@
         <v>710407.0</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C83" s="1">
         <v>10.0</v>
@@ -5737,16 +5767,16 @@
         <v>26</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M83" s="1" t="s">
         <v>26</v>
@@ -5760,7 +5790,7 @@
         <v>710120.0</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C84" s="1">
         <v>10.0</v>
@@ -5781,16 +5811,16 @@
         <v>26</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M84" s="1" t="s">
         <v>26</v>
@@ -5804,7 +5834,7 @@
         <v>711225.0</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C85" s="1">
         <v>10.0</v>
@@ -5825,10 +5855,10 @@
         <v>26</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K85" s="1" t="s">
         <v>18</v>
@@ -5848,16 +5878,16 @@
         <v>711282.0</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C86" s="1">
         <v>5.0</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F86" s="1">
         <v>711225.0</v>
@@ -5869,16 +5899,16 @@
         <v>26</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K86" s="1" t="s">
         <v>18</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M86" s="1" t="s">
         <v>26</v>
@@ -5892,7 +5922,7 @@
         <v>711265.0</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C87" s="1">
         <v>10.0</v>
@@ -5901,7 +5931,7 @@
         <v>15</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F87" s="1">
         <v>711225.0</v>
@@ -5913,16 +5943,16 @@
         <v>26</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M87" s="1" t="s">
         <v>26</v>
@@ -5936,7 +5966,7 @@
         <v>713780.0</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C88" s="1">
         <v>10.0</v>
@@ -5945,7 +5975,7 @@
         <v>15</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F88" s="1">
         <v>713760.0</v>
@@ -5957,13 +5987,13 @@
         <v>26</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L88" s="1" t="s">
         <v>30</v>
@@ -5980,7 +6010,7 @@
         <v>713742.0</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C89" s="1">
         <v>10.0</v>
@@ -5989,7 +6019,7 @@
         <v>15</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F89" s="1">
         <v>713760.0</v>
@@ -6004,13 +6034,13 @@
         <v>27</v>
       </c>
       <c r="J89" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M89" s="1" t="s">
         <v>26</v>
@@ -6024,7 +6054,7 @@
         <v>713735.0</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C90" s="1">
         <v>10.0</v>
@@ -6033,7 +6063,7 @@
         <v>15</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F90" s="1">
         <v>713760.0</v>
@@ -6048,10 +6078,10 @@
         <v>27</v>
       </c>
       <c r="J90" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L90" s="1" t="s">
         <v>30</v>
@@ -6068,7 +6098,7 @@
         <v>713784.0</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C91" s="1">
         <v>10.0</v>
@@ -6077,7 +6107,7 @@
         <v>15</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F91" s="1">
         <v>797060.0</v>
@@ -6092,13 +6122,13 @@
         <v>27</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M91" s="1" t="s">
         <v>26</v>
@@ -6112,7 +6142,7 @@
         <v>711249.0</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C92" s="1">
         <v>10.0</v>
@@ -6121,7 +6151,7 @@
         <v>15</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F92" s="1">
         <v>711225.0</v>
@@ -6133,16 +6163,16 @@
         <v>26</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K92" s="1" t="s">
         <v>18</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M92" s="1" t="s">
         <v>26</v>
@@ -6156,7 +6186,7 @@
         <v>711226.0</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C93" s="1">
         <v>10.0</v>
@@ -6165,7 +6195,7 @@
         <v>15</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F93" s="1">
         <v>711225.0</v>
@@ -6177,16 +6207,16 @@
         <v>26</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K93" s="1" t="s">
         <v>18</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M93" s="1" t="s">
         <v>26</v>
@@ -6200,7 +6230,7 @@
         <v>713760.0</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C94" s="1">
         <v>10.0</v>
@@ -6221,16 +6251,16 @@
         <v>26</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M94" s="1" t="s">
         <v>26</v>
@@ -6244,7 +6274,7 @@
         <v>713725.0</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C95" s="1">
         <v>10.0</v>
@@ -6253,7 +6283,7 @@
         <v>15</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F95" s="1">
         <v>713760.0</v>
@@ -6268,10 +6298,10 @@
         <v>20</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L95" s="1" t="s">
         <v>30</v>
@@ -6288,16 +6318,16 @@
         <v>713727.0</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C96" s="1">
         <v>5.0</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F96" s="1">
         <v>713760.0</v>
@@ -6312,7 +6342,7 @@
         <v>20</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K96" s="1" t="s">
         <v>18</v>
@@ -6332,7 +6362,7 @@
         <v>713757.0</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C97" s="1">
         <v>10.0</v>
@@ -6341,10 +6371,10 @@
         <v>15</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G97" s="1" t="s">
         <v>18</v>
@@ -6353,13 +6383,13 @@
         <v>19</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L97" s="1" t="s">
         <v>30</v>
@@ -6376,7 +6406,7 @@
         <v>713788.0</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C98" s="1">
         <v>10.0</v>
@@ -6385,7 +6415,7 @@
         <v>15</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>18</v>
@@ -6397,13 +6427,13 @@
         <v>19</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L98" s="1" t="s">
         <v>30</v>
@@ -6420,7 +6450,7 @@
         <v>713766.0</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C99" s="1">
         <v>10.0</v>
@@ -6429,10 +6459,10 @@
         <v>15</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G99" s="1">
         <v>797100.0</v>
@@ -6444,13 +6474,13 @@
         <v>27</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M99" s="1" t="s">
         <v>26</v>
@@ -6464,7 +6494,7 @@
         <v>713767.0</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C100" s="1">
         <v>10.0</v>
@@ -6473,10 +6503,10 @@
         <v>15</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G100" s="1">
         <v>797100.0</v>
@@ -6488,13 +6518,13 @@
         <v>27</v>
       </c>
       <c r="J100" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M100" s="1" t="s">
         <v>26</v>
@@ -6508,7 +6538,7 @@
         <v>713776.0</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C101" s="1">
         <v>10.0</v>
@@ -6517,13 +6547,13 @@
         <v>15</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H101" s="1" t="s">
         <v>19</v>
@@ -6532,10 +6562,10 @@
         <v>27</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K101" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L101" s="1" t="s">
         <v>30</v>
@@ -6552,7 +6582,7 @@
         <v>713764.0</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C102" s="1">
         <v>10.0</v>
@@ -6561,10 +6591,10 @@
         <v>15</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G102" s="1" t="s">
         <v>18</v>
@@ -6576,13 +6606,13 @@
         <v>27</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="K102" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M102" s="1" t="s">
         <v>26</v>
@@ -6596,7 +6626,7 @@
         <v>713771.0</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C103" s="1">
         <v>10.0</v>
@@ -6605,10 +6635,10 @@
         <v>15</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G103" s="1">
         <v>797251.0</v>
@@ -6620,10 +6650,10 @@
         <v>27</v>
       </c>
       <c r="J103" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K103" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L103" s="1" t="s">
         <v>30</v>
@@ -6640,7 +6670,7 @@
         <v>713733.0</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C104" s="1">
         <v>10.0</v>
@@ -6649,7 +6679,7 @@
         <v>15</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>18</v>
@@ -6664,7 +6694,7 @@
         <v>20</v>
       </c>
       <c r="J104" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K104" s="1" t="s">
         <v>18</v>
@@ -6684,7 +6714,7 @@
         <v>716607.0</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C105" s="1">
         <v>10.0</v>
@@ -6708,10 +6738,10 @@
         <v>27</v>
       </c>
       <c r="J105" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L105" s="1" t="s">
         <v>30</v>
@@ -6728,37 +6758,37 @@
         <v>716604.0</v>
       </c>
       <c r="B106" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C106" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="J106" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="K106" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="C106" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F106" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G106" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H106" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I106" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="J106" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="K106" s="1" t="s">
-        <v>345</v>
-      </c>
       <c r="L106" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M106" s="1" t="s">
         <v>26</v>
@@ -6772,7 +6802,7 @@
         <v>716208.0</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C107" s="1">
         <v>10.0</v>
@@ -6796,13 +6826,13 @@
         <v>20</v>
       </c>
       <c r="J107" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M107" s="1" t="s">
         <v>26</v>
@@ -6816,7 +6846,7 @@
         <v>716609.0</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C108" s="1">
         <v>10.0</v>
@@ -6825,7 +6855,7 @@
         <v>15</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>18</v>
@@ -6837,16 +6867,16 @@
         <v>26</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J108" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K108" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M108" s="1" t="s">
         <v>26</v>
@@ -6860,34 +6890,34 @@
         <v>716608.0</v>
       </c>
       <c r="B109" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C109" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H109" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I109" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="J109" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="K109" s="1" t="s">
         <v>355</v>
-      </c>
-      <c r="C109" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="F109" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G109" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H109" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I109" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="J109" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="K109" s="1" t="s">
-        <v>354</v>
       </c>
       <c r="L109" s="1">
         <v>12.0</v>
@@ -6904,16 +6934,16 @@
         <v>716605.0</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C110" s="1">
         <v>5.0</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>18</v>
@@ -6925,13 +6955,13 @@
         <v>26</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J110" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L110" s="1">
         <v>10.0</v>
@@ -6948,7 +6978,7 @@
         <v>716602.0</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C111" s="1">
         <v>10.0</v>
@@ -6957,7 +6987,7 @@
         <v>15</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>18</v>
@@ -6969,16 +6999,16 @@
         <v>26</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J111" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M111" s="1" t="s">
         <v>26</v>
@@ -6992,7 +7022,7 @@
         <v>716611.0</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C112" s="1">
         <v>10.0</v>
@@ -7001,7 +7031,7 @@
         <v>15</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>18</v>
@@ -7013,16 +7043,16 @@
         <v>26</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J112" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M112" s="1" t="s">
         <v>26</v>
@@ -7036,34 +7066,34 @@
         <v>716612.0</v>
       </c>
       <c r="B113" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C113" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I113" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="J113" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="K113" s="1" t="s">
         <v>364</v>
-      </c>
-      <c r="C113" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="F113" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G113" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H113" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I113" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J113" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="K113" s="1" t="s">
-        <v>363</v>
       </c>
       <c r="L113" s="3">
         <v>46307.0</v>
@@ -7080,7 +7110,7 @@
         <v>716600.0</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C114" s="1">
         <v>10.0</v>
@@ -7089,7 +7119,7 @@
         <v>15</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>18</v>
@@ -7101,16 +7131,16 @@
         <v>26</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J114" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K114" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L114" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M114" s="1" t="s">
         <v>26</v>
@@ -7124,37 +7154,37 @@
         <v>716601.0</v>
       </c>
       <c r="B115" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C115" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I115" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="J115" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="K115" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="C115" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="F115" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G115" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H115" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I115" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="J115" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="K115" s="1" t="s">
-        <v>368</v>
-      </c>
       <c r="L115" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M115" s="1" t="s">
         <v>26</v>
@@ -7168,7 +7198,7 @@
         <v>713785.0</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C116" s="1">
         <v>10.0</v>
@@ -7177,7 +7207,7 @@
         <v>15</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F116" s="1">
         <v>713760.0</v>
@@ -7189,16 +7219,16 @@
         <v>26</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J116" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K116" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L116" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M116" s="1" t="s">
         <v>26</v>
@@ -7212,7 +7242,7 @@
         <v>713737.0</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C117" s="1">
         <v>10.0</v>
@@ -7221,10 +7251,10 @@
         <v>15</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G117" s="1" t="s">
         <v>18</v>
@@ -7236,10 +7266,10 @@
         <v>20</v>
       </c>
       <c r="J117" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="K117" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L117" s="1">
         <v>12.0</v>
@@ -7256,7 +7286,7 @@
         <v>713736.0</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C118" s="1">
         <v>10.0</v>
@@ -7265,7 +7295,7 @@
         <v>15</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F118" s="1">
         <v>713785.0</v>
@@ -7277,13 +7307,13 @@
         <v>19</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J118" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L118" s="1" t="s">
         <v>30</v>
@@ -7297,10 +7327,10 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C119" s="1">
         <v>10.0</v>
@@ -7309,7 +7339,7 @@
         <v>15</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>18</v>
@@ -7324,7 +7354,7 @@
         <v>20</v>
       </c>
       <c r="J119" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="K119" s="1" t="s">
         <v>18</v>
@@ -7341,10 +7371,10 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C120" s="1">
         <v>10.0</v>
@@ -7353,7 +7383,7 @@
         <v>15</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>18</v>
@@ -7365,10 +7395,10 @@
         <v>26</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J120" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K120" s="1" t="s">
         <v>18</v>
@@ -7385,10 +7415,10 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C121" s="1">
         <v>10.0</v>
@@ -7397,7 +7427,7 @@
         <v>15</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>18</v>
@@ -7412,7 +7442,7 @@
         <v>27</v>
       </c>
       <c r="J121" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K121" s="1" t="s">
         <v>18</v>
@@ -7429,10 +7459,10 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C122" s="1">
         <v>10.0</v>
@@ -7456,10 +7486,10 @@
         <v>27</v>
       </c>
       <c r="J122" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K122" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L122" s="1">
         <v>12.0</v>
@@ -7473,37 +7503,37 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B123" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C123" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H123" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I123" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="J123" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="K123" s="1" t="s">
         <v>346</v>
-      </c>
-      <c r="C123" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F123" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G123" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H123" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I123" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="J123" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="K123" s="1" t="s">
-        <v>345</v>
       </c>
       <c r="L123" s="4">
         <v>41162.0</v>
@@ -7520,7 +7550,7 @@
         <v>716150.0</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C124" s="1">
         <v>10.0</v>
@@ -7544,10 +7574,10 @@
         <v>20</v>
       </c>
       <c r="J124" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="K124" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L124" s="1">
         <v>12.0</v>
@@ -7561,10 +7591,10 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C125" s="1">
         <v>10.0</v>
@@ -7588,7 +7618,7 @@
         <v>20</v>
       </c>
       <c r="J125" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K125" s="1" t="s">
         <v>18</v>
@@ -7605,10 +7635,10 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C126" s="1">
         <v>10.0</v>
@@ -7629,16 +7659,16 @@
         <v>26</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J126" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K126" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L126" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M126" s="1" t="s">
         <v>26</v>
@@ -7649,37 +7679,37 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C127" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H127" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I127" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="J127" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="K127" s="1" t="s">
         <v>406</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="C127" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F127" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G127" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H127" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I127" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="J127" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="K127" s="1" t="s">
-        <v>405</v>
       </c>
       <c r="L127" s="4">
         <v>41162.0</v>
@@ -7693,10 +7723,10 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C128" s="1">
         <v>10.0</v>
@@ -7720,10 +7750,10 @@
         <v>20</v>
       </c>
       <c r="J128" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K128" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L128" s="3">
         <v>46307.0</v>
@@ -7737,10 +7767,10 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C129" s="1">
         <v>10.0</v>
@@ -7749,7 +7779,7 @@
         <v>15</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>18</v>
@@ -7761,10 +7791,10 @@
         <v>26</v>
       </c>
       <c r="I129" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J129" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K129" s="1" t="s">
         <v>18</v>
@@ -7781,10 +7811,10 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C130" s="1">
         <v>10.0</v>
@@ -7793,7 +7823,7 @@
         <v>15</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>18</v>
@@ -7805,10 +7835,10 @@
         <v>26</v>
       </c>
       <c r="I130" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J130" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K130" s="1" t="s">
         <v>18</v>
@@ -7825,10 +7855,10 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C131" s="1">
         <v>10.0</v>
@@ -7837,7 +7867,7 @@
         <v>15</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>18</v>
@@ -7849,10 +7879,10 @@
         <v>26</v>
       </c>
       <c r="I131" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J131" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K131" s="1" t="s">
         <v>18</v>
@@ -7869,10 +7899,10 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C132" s="1">
         <v>10.0</v>
@@ -7881,7 +7911,7 @@
         <v>15</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>18</v>
@@ -7893,10 +7923,10 @@
         <v>26</v>
       </c>
       <c r="I132" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J132" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="K132" s="1" t="s">
         <v>18</v>
@@ -7913,19 +7943,19 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C133" s="1">
         <v>5.0</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>18</v>
@@ -7937,13 +7967,13 @@
         <v>26</v>
       </c>
       <c r="I133" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J133" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K133" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L133" s="1">
         <v>12.0</v>
@@ -7957,19 +7987,19 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C134" s="1">
         <v>5.0</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>18</v>
@@ -7981,13 +8011,13 @@
         <v>26</v>
       </c>
       <c r="I134" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J134" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K134" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L134" s="1">
         <v>12.0</v>
@@ -8001,37 +8031,37 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B135" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C135" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H135" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I135" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="J135" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="K135" s="1" t="s">
         <v>355</v>
-      </c>
-      <c r="C135" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E135" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="F135" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G135" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H135" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I135" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="J135" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="K135" s="1" t="s">
-        <v>354</v>
       </c>
       <c r="L135" s="1" t="s">
         <v>30</v>
@@ -8045,10 +8075,10 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C136" s="1">
         <v>10.0</v>
@@ -8057,7 +8087,7 @@
         <v>15</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>18</v>
@@ -8069,13 +8099,13 @@
         <v>26</v>
       </c>
       <c r="I136" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J136" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="K136" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L136" s="1">
         <v>12.0</v>
@@ -8092,7 +8122,7 @@
         <v>715179.0</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C137" s="1">
         <v>10.0</v>
@@ -8113,10 +8143,10 @@
         <v>26</v>
       </c>
       <c r="I137" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J137" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="K137" s="1" t="s">
         <v>22</v>
@@ -8136,7 +8166,7 @@
         <v>715178.0</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C138" s="1">
         <v>10.0</v>
@@ -8157,10 +8187,10 @@
         <v>26</v>
       </c>
       <c r="I138" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J138" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K138" s="1" t="s">
         <v>22</v>
@@ -8180,7 +8210,7 @@
         <v>715118.0</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C139" s="1">
         <v>10.0</v>
@@ -8189,7 +8219,7 @@
         <v>15</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F139" s="1">
         <v>715117.0</v>
@@ -8201,10 +8231,10 @@
         <v>26</v>
       </c>
       <c r="I139" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J139" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K139" s="1" t="s">
         <v>22</v>
@@ -8216,7 +8246,7 @@
         <v>19</v>
       </c>
       <c r="N139" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="140">
@@ -8224,13 +8254,13 @@
         <v>715190.0</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C140" s="1">
         <v>5.0</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>18</v>
@@ -8248,19 +8278,19 @@
         <v>20</v>
       </c>
       <c r="J140" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="K140" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M140" s="1" t="s">
         <v>19</v>
       </c>
       <c r="N140" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="141">
@@ -8268,7 +8298,7 @@
         <v>715170.0</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C141" s="1">
         <v>10.0</v>
@@ -8292,7 +8322,7 @@
         <v>20</v>
       </c>
       <c r="J141" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="K141" s="1" t="s">
         <v>22</v>
@@ -8304,7 +8334,7 @@
         <v>19</v>
       </c>
       <c r="N141" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="142">
@@ -8312,7 +8342,7 @@
         <v>715236.0</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C142" s="1">
         <v>10.0</v>
@@ -8336,7 +8366,7 @@
         <v>20</v>
       </c>
       <c r="J142" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K142" s="1" t="s">
         <v>22</v>
@@ -8356,7 +8386,7 @@
         <v>715117.0</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C143" s="1">
         <v>10.0</v>
@@ -8380,7 +8410,7 @@
         <v>20</v>
       </c>
       <c r="J143" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="K143" s="1" t="s">
         <v>22</v>
@@ -8392,7 +8422,7 @@
         <v>19</v>
       </c>
       <c r="N143" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="144">
@@ -8400,7 +8430,7 @@
         <v>715195.0</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C144" s="1">
         <v>10.0</v>
@@ -8424,13 +8454,13 @@
         <v>20</v>
       </c>
       <c r="J144" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="K144" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L144" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M144" s="1" t="s">
         <v>19</v>
@@ -8444,7 +8474,7 @@
         <v>715194.0</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C145" s="1">
         <v>10.0</v>
@@ -8468,13 +8498,13 @@
         <v>20</v>
       </c>
       <c r="J145" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="K145" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L145" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M145" s="1" t="s">
         <v>19</v>
@@ -8488,7 +8518,7 @@
         <v>715200.0</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C146" s="1">
         <v>10.0</v>
@@ -8497,7 +8527,7 @@
         <v>15</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F146" s="1">
         <v>715194.0</v>
@@ -8512,7 +8542,7 @@
         <v>20</v>
       </c>
       <c r="J146" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="K146" s="1" t="s">
         <v>22</v>
@@ -8532,7 +8562,7 @@
         <v>715101.0</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C147" s="1">
         <v>10.0</v>
@@ -8556,7 +8586,7 @@
         <v>20</v>
       </c>
       <c r="J147" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K147" s="1" t="s">
         <v>22</v>
@@ -8576,7 +8606,7 @@
         <v>715103.0</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C148" s="1">
         <v>10.0</v>
@@ -8600,7 +8630,7 @@
         <v>20</v>
       </c>
       <c r="J148" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K148" s="1" t="s">
         <v>22</v>
@@ -8620,7 +8650,7 @@
         <v>715104.0</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C149" s="1">
         <v>10.0</v>
@@ -8644,19 +8674,19 @@
         <v>20</v>
       </c>
       <c r="J149" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="K149" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L149" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M149" s="1" t="s">
         <v>19</v>
       </c>
       <c r="N149" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="150">
@@ -8664,7 +8694,7 @@
         <v>715106.0</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C150" s="1">
         <v>10.0</v>
@@ -8676,7 +8706,7 @@
         <v>18</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="G150" s="1" t="s">
         <v>18</v>
@@ -8688,7 +8718,7 @@
         <v>20</v>
       </c>
       <c r="J150" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="K150" s="1" t="s">
         <v>22</v>
@@ -8700,7 +8730,7 @@
         <v>19</v>
       </c>
       <c r="N150" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="151">
@@ -8708,7 +8738,7 @@
         <v>715188.0</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C151" s="1">
         <v>10.0</v>
@@ -8717,7 +8747,7 @@
         <v>15</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>18</v>
@@ -8732,7 +8762,7 @@
         <v>20</v>
       </c>
       <c r="J151" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="K151" s="1" t="s">
         <v>22</v>
@@ -8744,7 +8774,7 @@
         <v>19</v>
       </c>
       <c r="N151" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="152">
@@ -8752,7 +8782,7 @@
         <v>715189.0</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C152" s="1">
         <v>10.0</v>
@@ -8761,7 +8791,7 @@
         <v>15</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>18</v>
@@ -8776,7 +8806,7 @@
         <v>20</v>
       </c>
       <c r="J152" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K152" s="1" t="s">
         <v>22</v>
@@ -8788,7 +8818,7 @@
         <v>19</v>
       </c>
       <c r="N152" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="153">
@@ -8796,7 +8826,7 @@
         <v>724000.0</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C153" s="1">
         <v>10.0</v>
@@ -8817,16 +8847,16 @@
         <v>26</v>
       </c>
       <c r="I153" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J153" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="K153" s="1" t="s">
         <v>18</v>
       </c>
       <c r="L153" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M153" s="1" t="s">
         <v>26</v>
@@ -8840,7 +8870,7 @@
         <v>715800.0</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C154" s="1">
         <v>10.0</v>
@@ -8849,7 +8879,7 @@
         <v>15</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>18</v>
@@ -8861,13 +8891,13 @@
         <v>19</v>
       </c>
       <c r="I154" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J154" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="K154" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L154" s="1" t="s">
         <v>30</v>
@@ -8884,7 +8914,7 @@
         <v>724220.0</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C155" s="1">
         <v>10.0</v>
@@ -8893,7 +8923,7 @@
         <v>15</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>18</v>
@@ -8905,16 +8935,16 @@
         <v>19</v>
       </c>
       <c r="I155" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J155" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="K155" s="1" t="s">
         <v>18</v>
       </c>
       <c r="L155" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M155" s="1" t="s">
         <v>26</v>
@@ -8928,7 +8958,7 @@
         <v>753331.0</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C156" s="1">
         <v>10.0</v>
@@ -8949,16 +8979,16 @@
         <v>26</v>
       </c>
       <c r="I156" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J156" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K156" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L156" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M156" s="1" t="s">
         <v>26</v>
@@ -8972,7 +9002,7 @@
         <v>753333.0</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C157" s="1">
         <v>10.0</v>
@@ -8981,7 +9011,7 @@
         <v>15</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F157" s="1">
         <v>753331.0</v>
@@ -8993,16 +9023,16 @@
         <v>19</v>
       </c>
       <c r="I157" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J157" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K157" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L157" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M157" s="1" t="s">
         <v>26</v>
@@ -9016,7 +9046,7 @@
         <v>724200.0</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C158" s="1">
         <v>10.0</v>
@@ -9037,16 +9067,16 @@
         <v>26</v>
       </c>
       <c r="I158" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J158" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K158" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L158" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M158" s="1" t="s">
         <v>26</v>
@@ -9060,7 +9090,7 @@
         <v>724600.0</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C159" s="1">
         <v>10.0</v>
@@ -9081,16 +9111,16 @@
         <v>26</v>
       </c>
       <c r="I159" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J159" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="K159" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L159" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M159" s="1" t="s">
         <v>26</v>
@@ -9104,7 +9134,7 @@
         <v>715237.0</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C160" s="1">
         <v>10.0</v>
@@ -9128,7 +9158,7 @@
         <v>20</v>
       </c>
       <c r="J160" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="K160" s="1" t="s">
         <v>22</v>
@@ -9148,7 +9178,7 @@
         <v>715238.0</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C161" s="1">
         <v>10.0</v>
@@ -9157,7 +9187,7 @@
         <v>15</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F161" s="1">
         <v>715237.0</v>
@@ -9172,10 +9202,10 @@
         <v>20</v>
       </c>
       <c r="J161" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K161" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L161" s="1">
         <v>12.0</v>
@@ -9192,7 +9222,7 @@
         <v>715112.0</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C162" s="1">
         <v>10.0</v>
@@ -9216,7 +9246,7 @@
         <v>20</v>
       </c>
       <c r="J162" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="K162" s="1" t="s">
         <v>22</v>
@@ -9236,7 +9266,7 @@
         <v>715173.0</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C163" s="1">
         <v>10.0</v>
@@ -9260,13 +9290,13 @@
         <v>20</v>
       </c>
       <c r="J163" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="K163" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L163" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M163" s="1" t="s">
         <v>19</v>
@@ -9280,7 +9310,7 @@
         <v>715193.0</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C164" s="1">
         <v>10.0</v>
@@ -9304,13 +9334,13 @@
         <v>20</v>
       </c>
       <c r="J164" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="K164" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L164" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M164" s="1" t="s">
         <v>19</v>
@@ -9324,7 +9354,7 @@
         <v>715171.0</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C165" s="1">
         <v>10.0</v>
@@ -9348,13 +9378,13 @@
         <v>20</v>
       </c>
       <c r="J165" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="K165" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L165" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M165" s="1" t="s">
         <v>19</v>
@@ -9368,7 +9398,7 @@
         <v>724441.0</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C166" s="1">
         <v>10.0</v>
@@ -9377,7 +9407,7 @@
         <v>15</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F166" s="1">
         <v>724000.0</v>
@@ -9389,16 +9419,16 @@
         <v>19</v>
       </c>
       <c r="I166" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J166" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="K166" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="L166" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M166" s="1" t="s">
         <v>26</v>
@@ -9412,7 +9442,7 @@
         <v>724443.0</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C167" s="1">
         <v>10.0</v>
@@ -9421,7 +9451,7 @@
         <v>15</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>18</v>
@@ -9433,16 +9463,16 @@
         <v>19</v>
       </c>
       <c r="I167" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J167" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="K167" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="L167" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M167" s="1" t="s">
         <v>26</v>
@@ -9456,7 +9486,7 @@
         <v>724444.0</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C168" s="1">
         <v>10.0</v>
@@ -9465,7 +9495,7 @@
         <v>15</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>18</v>
@@ -9477,13 +9507,13 @@
         <v>19</v>
       </c>
       <c r="I168" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J168" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="K168" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="L168" s="1" t="s">
         <v>30</v>
@@ -9500,7 +9530,7 @@
         <v>724300.0</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C169" s="1">
         <v>10.0</v>
@@ -9521,16 +9551,16 @@
         <v>26</v>
       </c>
       <c r="I169" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J169" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="K169" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="L169" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M169" s="1" t="s">
         <v>26</v>
@@ -9544,7 +9574,7 @@
         <v>724310.0</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C170" s="1">
         <v>10.0</v>
@@ -9553,7 +9583,7 @@
         <v>15</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F170" s="1">
         <v>724300.0</v>
@@ -9565,16 +9595,16 @@
         <v>26</v>
       </c>
       <c r="I170" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J170" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="K170" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="L170" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M170" s="1" t="s">
         <v>26</v>
@@ -9588,7 +9618,7 @@
         <v>724311.0</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C171" s="1">
         <v>10.0</v>
@@ -9597,10 +9627,10 @@
         <v>15</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="G171" s="1" t="s">
         <v>18</v>
@@ -9609,13 +9639,13 @@
         <v>19</v>
       </c>
       <c r="I171" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J171" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="K171" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="L171" s="1" t="s">
         <v>30</v>
@@ -9632,7 +9662,7 @@
         <v>765000.0</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C172" s="1">
         <v>10.0</v>
@@ -9653,16 +9683,16 @@
         <v>26</v>
       </c>
       <c r="I172" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J172" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="K172" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L172" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M172" s="1" t="s">
         <v>26</v>
@@ -9676,7 +9706,7 @@
         <v>765020.0</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C173" s="1">
         <v>10.0</v>
@@ -9685,7 +9715,7 @@
         <v>15</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F173" s="1">
         <v>765000.0</v>
@@ -9697,16 +9727,16 @@
         <v>26</v>
       </c>
       <c r="I173" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J173" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="K173" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="L173" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M173" s="1" t="s">
         <v>26</v>
@@ -9720,7 +9750,7 @@
         <v>765040.0</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C174" s="1">
         <v>10.0</v>
@@ -9729,7 +9759,7 @@
         <v>15</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="F174" s="1">
         <v>765020.0</v>
@@ -9741,16 +9771,16 @@
         <v>26</v>
       </c>
       <c r="I174" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J174" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="K174" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L174" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M174" s="1" t="s">
         <v>26</v>
@@ -9764,7 +9794,7 @@
         <v>765060.0</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C175" s="1">
         <v>10.0</v>
@@ -9773,7 +9803,7 @@
         <v>15</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F175" s="1">
         <v>765060.0</v>
@@ -9785,16 +9815,16 @@
         <v>19</v>
       </c>
       <c r="I175" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J175" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="K175" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L175" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M175" s="1" t="s">
         <v>26</v>
@@ -9808,7 +9838,7 @@
         <v>765315.0</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C176" s="1">
         <v>10.0</v>
@@ -9817,7 +9847,7 @@
         <v>15</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F176" s="1">
         <v>765310.0</v>
@@ -9829,16 +9859,16 @@
         <v>26</v>
       </c>
       <c r="I176" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J176" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="K176" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L176" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M176" s="1" t="s">
         <v>26</v>
@@ -9852,7 +9882,7 @@
         <v>765320.0</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C177" s="1">
         <v>10.0</v>
@@ -9861,7 +9891,7 @@
         <v>15</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F177" s="1">
         <v>765315.0</v>
@@ -9873,16 +9903,16 @@
         <v>19</v>
       </c>
       <c r="I177" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J177" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="K177" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L177" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M177" s="1" t="s">
         <v>26</v>
@@ -9896,7 +9926,7 @@
         <v>765325.0</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C178" s="1">
         <v>10.0</v>
@@ -9905,7 +9935,7 @@
         <v>15</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F178" s="1">
         <v>765320.0</v>
@@ -9917,16 +9947,16 @@
         <v>19</v>
       </c>
       <c r="I178" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J178" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K178" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L178" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M178" s="1" t="s">
         <v>26</v>
@@ -9940,7 +9970,7 @@
         <v>765300.0</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C179" s="1">
         <v>10.0</v>
@@ -9961,16 +9991,16 @@
         <v>26</v>
       </c>
       <c r="I179" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J179" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="K179" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L179" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M179" s="1" t="s">
         <v>26</v>
@@ -9984,7 +10014,7 @@
         <v>765310.0</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C180" s="1">
         <v>10.0</v>
@@ -9993,7 +10023,7 @@
         <v>15</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="F180" s="1">
         <v>765310.0</v>
@@ -10005,16 +10035,16 @@
         <v>26</v>
       </c>
       <c r="I180" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J180" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="K180" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L180" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M180" s="1" t="s">
         <v>26</v>
@@ -10028,7 +10058,7 @@
         <v>765100.0</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C181" s="1">
         <v>10.0</v>
@@ -10037,7 +10067,7 @@
         <v>15</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>18</v>
@@ -10049,16 +10079,16 @@
         <v>26</v>
       </c>
       <c r="I181" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J181" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="K181" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L181" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M181" s="1" t="s">
         <v>26</v>
@@ -10072,7 +10102,7 @@
         <v>765120.0</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C182" s="1">
         <v>10.0</v>
@@ -10081,7 +10111,7 @@
         <v>15</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="F182" s="1">
         <v>765100.0</v>
@@ -10093,16 +10123,16 @@
         <v>26</v>
       </c>
       <c r="I182" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J182" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="K182" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L182" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M182" s="1" t="s">
         <v>26</v>
@@ -10116,7 +10146,7 @@
         <v>765140.0</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C183" s="1">
         <v>10.0</v>
@@ -10125,7 +10155,7 @@
         <v>15</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F183" s="1">
         <v>765120.0</v>
@@ -10137,16 +10167,16 @@
         <v>26</v>
       </c>
       <c r="I183" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J183" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="K183" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L183" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M183" s="1" t="s">
         <v>26</v>
@@ -10160,7 +10190,7 @@
         <v>765162.0</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C184" s="1">
         <v>10.0</v>
@@ -10169,7 +10199,7 @@
         <v>15</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="F184" s="1">
         <v>765140.0</v>
@@ -10181,16 +10211,16 @@
         <v>19</v>
       </c>
       <c r="I184" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J184" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="K184" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L184" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M184" s="1" t="s">
         <v>26</v>
@@ -10204,7 +10234,7 @@
         <v>765191.0</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C185" s="1">
         <v>10.0</v>
@@ -10213,7 +10243,7 @@
         <v>15</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F185" s="1">
         <v>765162.0</v>
@@ -10225,16 +10255,16 @@
         <v>19</v>
       </c>
       <c r="I185" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J185" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="K185" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L185" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M185" s="1" t="s">
         <v>26</v>
@@ -10248,7 +10278,7 @@
         <v>765080.0</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C186" s="1">
         <v>10.0</v>
@@ -10257,7 +10287,7 @@
         <v>15</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F186" s="1">
         <v>765060.0</v>
@@ -10269,10 +10299,10 @@
         <v>19</v>
       </c>
       <c r="I186" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J186" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="K186" s="1" t="s">
         <v>22</v>
@@ -10292,7 +10322,7 @@
         <v>765400.0</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C187" s="1">
         <v>10.0</v>
@@ -10313,16 +10343,16 @@
         <v>26</v>
       </c>
       <c r="I187" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J187" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="K187" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L187" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M187" s="1" t="s">
         <v>26</v>
@@ -10336,7 +10366,7 @@
         <v>765401.0</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C188" s="1">
         <v>10.0</v>
@@ -10345,7 +10375,7 @@
         <v>15</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="F188" s="1">
         <v>765400.0</v>
@@ -10357,16 +10387,16 @@
         <v>26</v>
       </c>
       <c r="I188" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J188" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="K188" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L188" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M188" s="1" t="s">
         <v>26</v>
@@ -10380,7 +10410,7 @@
         <v>765402.0</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C189" s="1">
         <v>10.0</v>
@@ -10389,7 +10419,7 @@
         <v>15</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="F189" s="1">
         <v>765401.0</v>
@@ -10401,16 +10431,16 @@
         <v>26</v>
       </c>
       <c r="I189" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J189" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="K189" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L189" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M189" s="1" t="s">
         <v>26</v>
@@ -10424,7 +10454,7 @@
         <v>714824.0</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C190" s="1">
         <v>10.0</v>
@@ -10445,13 +10475,13 @@
         <v>19</v>
       </c>
       <c r="I190" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J190" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="K190" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="L190" s="1">
         <v>12.0</v>
@@ -10468,7 +10498,7 @@
         <v>797253.0</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C191" s="1">
         <v>10.0</v>
@@ -10477,10 +10507,10 @@
         <v>15</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G191" s="1" t="s">
         <v>18</v>
@@ -10489,13 +10519,13 @@
         <v>26</v>
       </c>
       <c r="I191" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J191" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="K191" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="L191" s="1" t="s">
         <v>30</v>
@@ -10512,7 +10542,7 @@
         <v>797256.0</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C192" s="1">
         <v>10.0</v>
@@ -10521,10 +10551,10 @@
         <v>15</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="G192" s="1" t="s">
         <v>18</v>
@@ -10533,13 +10563,13 @@
         <v>26</v>
       </c>
       <c r="I192" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J192" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="K192" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="L192" s="1" t="s">
         <v>30</v>
@@ -10556,7 +10586,7 @@
         <v>710418.0</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C193" s="1">
         <v>10.0</v>
@@ -10577,16 +10607,16 @@
         <v>26</v>
       </c>
       <c r="I193" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J193" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="K193" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="L193" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M193" s="1" t="s">
         <v>26</v>
@@ -10600,7 +10630,7 @@
         <v>711267.0</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C194" s="1">
         <v>10.0</v>
@@ -10609,10 +10639,10 @@
         <v>15</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="G194" s="1" t="s">
         <v>18</v>
@@ -10621,16 +10651,16 @@
         <v>26</v>
       </c>
       <c r="I194" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J194" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="K194" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="L194" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M194" s="1" t="s">
         <v>26</v>
@@ -10644,7 +10674,7 @@
         <v>711291.0</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C195" s="1">
         <v>10.0</v>
@@ -10653,7 +10683,7 @@
         <v>15</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="F195" s="1">
         <v>711225.0</v>
@@ -10665,16 +10695,16 @@
         <v>26</v>
       </c>
       <c r="I195" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J195" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K195" s="1" t="s">
         <v>18</v>
       </c>
       <c r="L195" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M195" s="1" t="s">
         <v>26</v>
@@ -10688,16 +10718,16 @@
         <v>711227.0</v>
       </c>
       <c r="B196" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="C196" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D196" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E196" s="1" t="s">
         <v>597</v>
-      </c>
-      <c r="C196" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="D196" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E196" s="1" t="s">
-        <v>596</v>
       </c>
       <c r="F196" s="1">
         <v>711225.0</v>
@@ -10709,16 +10739,16 @@
         <v>26</v>
       </c>
       <c r="I196" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J196" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="K196" s="1" t="s">
         <v>18</v>
       </c>
       <c r="L196" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M196" s="1" t="s">
         <v>26</v>
@@ -10732,7 +10762,7 @@
         <v>715102.0</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C197" s="1">
         <v>10.0</v>
@@ -10741,7 +10771,7 @@
         <v>15</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F197" s="1">
         <v>715101.0</v>
@@ -10756,7 +10786,7 @@
         <v>20</v>
       </c>
       <c r="J197" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="K197" s="1" t="s">
         <v>22</v>
@@ -10773,10 +10803,10 @@
     </row>
     <row r="198">
       <c r="A198" s="2" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C198" s="1">
         <v>10.0</v>
@@ -10785,7 +10815,7 @@
         <v>15</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>18</v>
@@ -10797,21 +10827,109 @@
         <v>26</v>
       </c>
       <c r="I198" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J198" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="K198" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L198" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M198" s="1" t="s">
         <v>26</v>
       </c>
       <c r="N198" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="C199" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="D199" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="E199" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F199" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G199" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H199" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I199" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="J199" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="K199" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L199" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="M199" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N199" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="C200" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F200" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G200" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H200" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I200" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="J200" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="K200" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L200" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="M200" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N200" s="1" t="s">
         <v>36</v>
       </c>
     </row>
